--- a/010-npm_node/02-results/2212JPI01S Jefferson Loyd Park Ph. 1 Signage REV 4.xlsx
+++ b/010-npm_node/02-results/2212JPI01S Jefferson Loyd Park Ph. 1 Signage REV 4.xlsx
@@ -464,7 +464,7 @@
         <v>CONTACT</v>
       </c>
       <c r="I2" t="str">
-        <v>CONTRACT_NUMBER</v>
+        <v>CONTRACT</v>
       </c>
       <c r="J2" t="str">
         <v>REVISIONS</v>
@@ -476,7 +476,7 @@
         <v>CONTRACT_FILE</v>
       </c>
     </row>
-    <row r="3">
+    <row r="3" xml:space="preserve">
       <c r="A3" t="str">
         <v>#1: ENTRY SIGNAGE</v>
       </c>
@@ -504,8 +504,12 @@
       <c r="I3" t="str">
         <v>2212JPI01S</v>
       </c>
-      <c r="J3" t="str">
-        <v>01.06.23 03.20.23 REV 1 01.15.24 REV 2 03.28.24 REV 3 04.02.24 REV 4 (W/ADD ALT 1 SIGNAGE)</v>
+      <c r="J3" t="str" xml:space="preserve">
+        <v xml:space="preserve">01.06.23 03.20.23 REV 1
+ 01.15.24 REV 2
+ 03.28.24 REV 3
+ 04.02.24 REV 4
+ (W/ADD ALT 1 SIGNAGE)</v>
       </c>
       <c r="K3" t="str">
         <v>JEFFERSON LOYD PARK PH 1.</v>
@@ -514,7 +518,7 @@
         <v>2212JPI01S Jefferson Loyd Park Ph. 1 Signage REV 4.xlsx</v>
       </c>
     </row>
-    <row r="4">
+    <row r="4" xml:space="preserve">
       <c r="A4" t="str">
         <v>#1: ENTRY SIGNAGE</v>
       </c>
@@ -542,8 +546,12 @@
       <c r="I4" t="str">
         <v>2212JPI01S</v>
       </c>
-      <c r="J4" t="str">
-        <v>01.06.23 03.20.23 REV 1 01.15.24 REV 2 03.28.24 REV 3 04.02.24 REV 4 (W/ADD ALT 1 SIGNAGE)</v>
+      <c r="J4" t="str" xml:space="preserve">
+        <v xml:space="preserve">01.06.23 03.20.23 REV 1
+ 01.15.24 REV 2
+ 03.28.24 REV 3
+ 04.02.24 REV 4
+ (W/ADD ALT 1 SIGNAGE)</v>
       </c>
       <c r="K4" t="str">
         <v>JEFFERSON LOYD PARK PH 1.</v>
@@ -552,7 +560,7 @@
         <v>2212JPI01S Jefferson Loyd Park Ph. 1 Signage REV 4.xlsx</v>
       </c>
     </row>
-    <row r="5">
+    <row r="5" xml:space="preserve">
       <c r="A5" t="str">
         <v>#1: ENTRY SIGNAGE</v>
       </c>
@@ -580,8 +588,12 @@
       <c r="I5" t="str">
         <v>2212JPI01S</v>
       </c>
-      <c r="J5" t="str">
-        <v>01.06.23 03.20.23 REV 1 01.15.24 REV 2 03.28.24 REV 3 04.02.24 REV 4 (W/ADD ALT 1 SIGNAGE)</v>
+      <c r="J5" t="str" xml:space="preserve">
+        <v xml:space="preserve">01.06.23 03.20.23 REV 1
+ 01.15.24 REV 2
+ 03.28.24 REV 3
+ 04.02.24 REV 4
+ (W/ADD ALT 1 SIGNAGE)</v>
       </c>
       <c r="K5" t="str">
         <v>JEFFERSON LOYD PARK PH 1.</v>
@@ -590,7 +602,7 @@
         <v>2212JPI01S Jefferson Loyd Park Ph. 1 Signage REV 4.xlsx</v>
       </c>
     </row>
-    <row r="6">
+    <row r="6" xml:space="preserve">
       <c r="A6" t="str">
         <v>#2: LEASING CENTER- EXTERIOR SIGNAGE</v>
       </c>
@@ -618,8 +630,12 @@
       <c r="I6" t="str">
         <v>2212JPI01S</v>
       </c>
-      <c r="J6" t="str">
-        <v>01.06.23 03.20.23 REV 1 01.15.24 REV 2 03.28.24 REV 3 04.02.24 REV 4 (W/ADD ALT 1 SIGNAGE)</v>
+      <c r="J6" t="str" xml:space="preserve">
+        <v xml:space="preserve">01.06.23 03.20.23 REV 1
+ 01.15.24 REV 2
+ 03.28.24 REV 3
+ 04.02.24 REV 4
+ (W/ADD ALT 1 SIGNAGE)</v>
       </c>
       <c r="K6" t="str">
         <v>JEFFERSON LOYD PARK PH 1.</v>
@@ -628,7 +644,7 @@
         <v>2212JPI01S Jefferson Loyd Park Ph. 1 Signage REV 4.xlsx</v>
       </c>
     </row>
-    <row r="7">
+    <row r="7" xml:space="preserve">
       <c r="A7" t="str">
         <v>#2: LEASING CENTER- EXTERIOR SIGNAGE</v>
       </c>
@@ -656,8 +672,12 @@
       <c r="I7" t="str">
         <v>2212JPI01S</v>
       </c>
-      <c r="J7" t="str">
-        <v>01.06.23 03.20.23 REV 1 01.15.24 REV 2 03.28.24 REV 3 04.02.24 REV 4 (W/ADD ALT 1 SIGNAGE)</v>
+      <c r="J7" t="str" xml:space="preserve">
+        <v xml:space="preserve">01.06.23 03.20.23 REV 1
+ 01.15.24 REV 2
+ 03.28.24 REV 3
+ 04.02.24 REV 4
+ (W/ADD ALT 1 SIGNAGE)</v>
       </c>
       <c r="K7" t="str">
         <v>JEFFERSON LOYD PARK PH 1.</v>
@@ -666,7 +686,7 @@
         <v>2212JPI01S Jefferson Loyd Park Ph. 1 Signage REV 4.xlsx</v>
       </c>
     </row>
-    <row r="8">
+    <row r="8" xml:space="preserve">
       <c r="A8" t="str">
         <v>#2: LEASING CENTER- EXTERIOR SIGNAGE</v>
       </c>
@@ -694,8 +714,12 @@
       <c r="I8" t="str">
         <v>2212JPI01S</v>
       </c>
-      <c r="J8" t="str">
-        <v>01.06.23 03.20.23 REV 1 01.15.24 REV 2 03.28.24 REV 3 04.02.24 REV 4 (W/ADD ALT 1 SIGNAGE)</v>
+      <c r="J8" t="str" xml:space="preserve">
+        <v xml:space="preserve">01.06.23 03.20.23 REV 1
+ 01.15.24 REV 2
+ 03.28.24 REV 3
+ 04.02.24 REV 4
+ (W/ADD ALT 1 SIGNAGE)</v>
       </c>
       <c r="K8" t="str">
         <v>JEFFERSON LOYD PARK PH 1.</v>
@@ -704,7 +728,7 @@
         <v>2212JPI01S Jefferson Loyd Park Ph. 1 Signage REV 4.xlsx</v>
       </c>
     </row>
-    <row r="9">
+    <row r="9" xml:space="preserve">
       <c r="A9" t="str">
         <v>#2: LEASING CENTER- EXTERIOR SIGNAGE</v>
       </c>
@@ -732,8 +756,12 @@
       <c r="I9" t="str">
         <v>2212JPI01S</v>
       </c>
-      <c r="J9" t="str">
-        <v>01.06.23 03.20.23 REV 1 01.15.24 REV 2 03.28.24 REV 3 04.02.24 REV 4 (W/ADD ALT 1 SIGNAGE)</v>
+      <c r="J9" t="str" xml:space="preserve">
+        <v xml:space="preserve">01.06.23 03.20.23 REV 1
+ 01.15.24 REV 2
+ 03.28.24 REV 3
+ 04.02.24 REV 4
+ (W/ADD ALT 1 SIGNAGE)</v>
       </c>
       <c r="K9" t="str">
         <v>JEFFERSON LOYD PARK PH 1.</v>
@@ -742,7 +770,7 @@
         <v>2212JPI01S Jefferson Loyd Park Ph. 1 Signage REV 4.xlsx</v>
       </c>
     </row>
-    <row r="10">
+    <row r="10" xml:space="preserve">
       <c r="A10" t="str">
         <v>#2: LEASING CENTER- EXTERIOR SIGNAGE</v>
       </c>
@@ -770,8 +798,12 @@
       <c r="I10" t="str">
         <v>2212JPI01S</v>
       </c>
-      <c r="J10" t="str">
-        <v>01.06.23 03.20.23 REV 1 01.15.24 REV 2 03.28.24 REV 3 04.02.24 REV 4 (W/ADD ALT 1 SIGNAGE)</v>
+      <c r="J10" t="str" xml:space="preserve">
+        <v xml:space="preserve">01.06.23 03.20.23 REV 1
+ 01.15.24 REV 2
+ 03.28.24 REV 3
+ 04.02.24 REV 4
+ (W/ADD ALT 1 SIGNAGE)</v>
       </c>
       <c r="K10" t="str">
         <v>JEFFERSON LOYD PARK PH 1.</v>
@@ -780,7 +812,7 @@
         <v>2212JPI01S Jefferson Loyd Park Ph. 1 Signage REV 4.xlsx</v>
       </c>
     </row>
-    <row r="11">
+    <row r="11" xml:space="preserve">
       <c r="A11" t="str">
         <v>#2: LEASING CENTER- EXTERIOR SIGNAGE</v>
       </c>
@@ -808,8 +840,12 @@
       <c r="I11" t="str">
         <v>2212JPI01S</v>
       </c>
-      <c r="J11" t="str">
-        <v>01.06.23 03.20.23 REV 1 01.15.24 REV 2 03.28.24 REV 3 04.02.24 REV 4 (W/ADD ALT 1 SIGNAGE)</v>
+      <c r="J11" t="str" xml:space="preserve">
+        <v xml:space="preserve">01.06.23 03.20.23 REV 1
+ 01.15.24 REV 2
+ 03.28.24 REV 3
+ 04.02.24 REV 4
+ (W/ADD ALT 1 SIGNAGE)</v>
       </c>
       <c r="K11" t="str">
         <v>JEFFERSON LOYD PARK PH 1.</v>
@@ -818,7 +854,7 @@
         <v>2212JPI01S Jefferson Loyd Park Ph. 1 Signage REV 4.xlsx</v>
       </c>
     </row>
-    <row r="12">
+    <row r="12" xml:space="preserve">
       <c r="A12" t="str">
         <v>#2: LEASING CENTER- EXTERIOR SIGNAGE</v>
       </c>
@@ -846,8 +882,12 @@
       <c r="I12" t="str">
         <v>2212JPI01S</v>
       </c>
-      <c r="J12" t="str">
-        <v>01.06.23 03.20.23 REV 1 01.15.24 REV 2 03.28.24 REV 3 04.02.24 REV 4 (W/ADD ALT 1 SIGNAGE)</v>
+      <c r="J12" t="str" xml:space="preserve">
+        <v xml:space="preserve">01.06.23 03.20.23 REV 1
+ 01.15.24 REV 2
+ 03.28.24 REV 3
+ 04.02.24 REV 4
+ (W/ADD ALT 1 SIGNAGE)</v>
       </c>
       <c r="K12" t="str">
         <v>JEFFERSON LOYD PARK PH 1.</v>
@@ -856,7 +896,7 @@
         <v>2212JPI01S Jefferson Loyd Park Ph. 1 Signage REV 4.xlsx</v>
       </c>
     </row>
-    <row r="13">
+    <row r="13" xml:space="preserve">
       <c r="A13" t="str">
         <v>#2: LEASING CENTER- EXTERIOR SIGNAGE</v>
       </c>
@@ -884,8 +924,12 @@
       <c r="I13" t="str">
         <v>2212JPI01S</v>
       </c>
-      <c r="J13" t="str">
-        <v>01.06.23 03.20.23 REV 1 01.15.24 REV 2 03.28.24 REV 3 04.02.24 REV 4 (W/ADD ALT 1 SIGNAGE)</v>
+      <c r="J13" t="str" xml:space="preserve">
+        <v xml:space="preserve">01.06.23 03.20.23 REV 1
+ 01.15.24 REV 2
+ 03.28.24 REV 3
+ 04.02.24 REV 4
+ (W/ADD ALT 1 SIGNAGE)</v>
       </c>
       <c r="K13" t="str">
         <v>JEFFERSON LOYD PARK PH 1.</v>
@@ -894,7 +938,7 @@
         <v>2212JPI01S Jefferson Loyd Park Ph. 1 Signage REV 4.xlsx</v>
       </c>
     </row>
-    <row r="14">
+    <row r="14" xml:space="preserve">
       <c r="A14" t="str">
         <v xml:space="preserve">#3: LEASING CENTER - INTERIOR SIGNAGE </v>
       </c>
@@ -922,8 +966,12 @@
       <c r="I14" t="str">
         <v>2212JPI01S</v>
       </c>
-      <c r="J14" t="str">
-        <v>01.06.23 03.20.23 REV 1 01.15.24 REV 2 03.28.24 REV 3 04.02.24 REV 4 (W/ADD ALT 1 SIGNAGE)</v>
+      <c r="J14" t="str" xml:space="preserve">
+        <v xml:space="preserve">01.06.23 03.20.23 REV 1
+ 01.15.24 REV 2
+ 03.28.24 REV 3
+ 04.02.24 REV 4
+ (W/ADD ALT 1 SIGNAGE)</v>
       </c>
       <c r="K14" t="str">
         <v>JEFFERSON LOYD PARK PH 1.</v>
@@ -932,7 +980,7 @@
         <v>2212JPI01S Jefferson Loyd Park Ph. 1 Signage REV 4.xlsx</v>
       </c>
     </row>
-    <row r="15">
+    <row r="15" xml:space="preserve">
       <c r="A15" t="str">
         <v xml:space="preserve">#3: LEASING CENTER - INTERIOR SIGNAGE </v>
       </c>
@@ -960,8 +1008,12 @@
       <c r="I15" t="str">
         <v>2212JPI01S</v>
       </c>
-      <c r="J15" t="str">
-        <v>01.06.23 03.20.23 REV 1 01.15.24 REV 2 03.28.24 REV 3 04.02.24 REV 4 (W/ADD ALT 1 SIGNAGE)</v>
+      <c r="J15" t="str" xml:space="preserve">
+        <v xml:space="preserve">01.06.23 03.20.23 REV 1
+ 01.15.24 REV 2
+ 03.28.24 REV 3
+ 04.02.24 REV 4
+ (W/ADD ALT 1 SIGNAGE)</v>
       </c>
       <c r="K15" t="str">
         <v>JEFFERSON LOYD PARK PH 1.</v>
@@ -970,7 +1022,7 @@
         <v>2212JPI01S Jefferson Loyd Park Ph. 1 Signage REV 4.xlsx</v>
       </c>
     </row>
-    <row r="16">
+    <row r="16" xml:space="preserve">
       <c r="A16" t="str">
         <v xml:space="preserve">#3: LEASING CENTER - INTERIOR SIGNAGE </v>
       </c>
@@ -998,8 +1050,12 @@
       <c r="I16" t="str">
         <v>2212JPI01S</v>
       </c>
-      <c r="J16" t="str">
-        <v>01.06.23 03.20.23 REV 1 01.15.24 REV 2 03.28.24 REV 3 04.02.24 REV 4 (W/ADD ALT 1 SIGNAGE)</v>
+      <c r="J16" t="str" xml:space="preserve">
+        <v xml:space="preserve">01.06.23 03.20.23 REV 1
+ 01.15.24 REV 2
+ 03.28.24 REV 3
+ 04.02.24 REV 4
+ (W/ADD ALT 1 SIGNAGE)</v>
       </c>
       <c r="K16" t="str">
         <v>JEFFERSON LOYD PARK PH 1.</v>
@@ -1008,7 +1064,7 @@
         <v>2212JPI01S Jefferson Loyd Park Ph. 1 Signage REV 4.xlsx</v>
       </c>
     </row>
-    <row r="17">
+    <row r="17" xml:space="preserve">
       <c r="A17" t="str">
         <v xml:space="preserve">#3: LEASING CENTER - INTERIOR SIGNAGE </v>
       </c>
@@ -1036,8 +1092,12 @@
       <c r="I17" t="str">
         <v>2212JPI01S</v>
       </c>
-      <c r="J17" t="str">
-        <v>01.06.23 03.20.23 REV 1 01.15.24 REV 2 03.28.24 REV 3 04.02.24 REV 4 (W/ADD ALT 1 SIGNAGE)</v>
+      <c r="J17" t="str" xml:space="preserve">
+        <v xml:space="preserve">01.06.23 03.20.23 REV 1
+ 01.15.24 REV 2
+ 03.28.24 REV 3
+ 04.02.24 REV 4
+ (W/ADD ALT 1 SIGNAGE)</v>
       </c>
       <c r="K17" t="str">
         <v>JEFFERSON LOYD PARK PH 1.</v>
@@ -1046,7 +1106,7 @@
         <v>2212JPI01S Jefferson Loyd Park Ph. 1 Signage REV 4.xlsx</v>
       </c>
     </row>
-    <row r="18">
+    <row r="18" xml:space="preserve">
       <c r="A18" t="str">
         <v xml:space="preserve">#3: LEASING CENTER - INTERIOR SIGNAGE </v>
       </c>
@@ -1074,8 +1134,12 @@
       <c r="I18" t="str">
         <v>2212JPI01S</v>
       </c>
-      <c r="J18" t="str">
-        <v>01.06.23 03.20.23 REV 1 01.15.24 REV 2 03.28.24 REV 3 04.02.24 REV 4 (W/ADD ALT 1 SIGNAGE)</v>
+      <c r="J18" t="str" xml:space="preserve">
+        <v xml:space="preserve">01.06.23 03.20.23 REV 1
+ 01.15.24 REV 2
+ 03.28.24 REV 3
+ 04.02.24 REV 4
+ (W/ADD ALT 1 SIGNAGE)</v>
       </c>
       <c r="K18" t="str">
         <v>JEFFERSON LOYD PARK PH 1.</v>
@@ -1084,7 +1148,7 @@
         <v>2212JPI01S Jefferson Loyd Park Ph. 1 Signage REV 4.xlsx</v>
       </c>
     </row>
-    <row r="19">
+    <row r="19" xml:space="preserve">
       <c r="A19" t="str">
         <v xml:space="preserve">#3: LEASING CENTER - INTERIOR SIGNAGE </v>
       </c>
@@ -1112,8 +1176,12 @@
       <c r="I19" t="str">
         <v>2212JPI01S</v>
       </c>
-      <c r="J19" t="str">
-        <v>01.06.23 03.20.23 REV 1 01.15.24 REV 2 03.28.24 REV 3 04.02.24 REV 4 (W/ADD ALT 1 SIGNAGE)</v>
+      <c r="J19" t="str" xml:space="preserve">
+        <v xml:space="preserve">01.06.23 03.20.23 REV 1
+ 01.15.24 REV 2
+ 03.28.24 REV 3
+ 04.02.24 REV 4
+ (W/ADD ALT 1 SIGNAGE)</v>
       </c>
       <c r="K19" t="str">
         <v>JEFFERSON LOYD PARK PH 1.</v>
@@ -1122,7 +1190,7 @@
         <v>2212JPI01S Jefferson Loyd Park Ph. 1 Signage REV 4.xlsx</v>
       </c>
     </row>
-    <row r="20">
+    <row r="20" xml:space="preserve">
       <c r="A20" t="str">
         <v xml:space="preserve">#3: LEASING CENTER - INTERIOR SIGNAGE </v>
       </c>
@@ -1150,8 +1218,12 @@
       <c r="I20" t="str">
         <v>2212JPI01S</v>
       </c>
-      <c r="J20" t="str">
-        <v>01.06.23 03.20.23 REV 1 01.15.24 REV 2 03.28.24 REV 3 04.02.24 REV 4 (W/ADD ALT 1 SIGNAGE)</v>
+      <c r="J20" t="str" xml:space="preserve">
+        <v xml:space="preserve">01.06.23 03.20.23 REV 1
+ 01.15.24 REV 2
+ 03.28.24 REV 3
+ 04.02.24 REV 4
+ (W/ADD ALT 1 SIGNAGE)</v>
       </c>
       <c r="K20" t="str">
         <v>JEFFERSON LOYD PARK PH 1.</v>
@@ -1160,7 +1232,7 @@
         <v>2212JPI01S Jefferson Loyd Park Ph. 1 Signage REV 4.xlsx</v>
       </c>
     </row>
-    <row r="21">
+    <row r="21" xml:space="preserve">
       <c r="A21" t="str">
         <v xml:space="preserve">#3: LEASING CENTER - INTERIOR SIGNAGE </v>
       </c>
@@ -1188,8 +1260,12 @@
       <c r="I21" t="str">
         <v>2212JPI01S</v>
       </c>
-      <c r="J21" t="str">
-        <v>01.06.23 03.20.23 REV 1 01.15.24 REV 2 03.28.24 REV 3 04.02.24 REV 4 (W/ADD ALT 1 SIGNAGE)</v>
+      <c r="J21" t="str" xml:space="preserve">
+        <v xml:space="preserve">01.06.23 03.20.23 REV 1
+ 01.15.24 REV 2
+ 03.28.24 REV 3
+ 04.02.24 REV 4
+ (W/ADD ALT 1 SIGNAGE)</v>
       </c>
       <c r="K21" t="str">
         <v>JEFFERSON LOYD PARK PH 1.</v>
@@ -1198,7 +1274,7 @@
         <v>2212JPI01S Jefferson Loyd Park Ph. 1 Signage REV 4.xlsx</v>
       </c>
     </row>
-    <row r="22">
+    <row r="22" xml:space="preserve">
       <c r="A22" t="str">
         <v xml:space="preserve">#3: LEASING CENTER - INTERIOR SIGNAGE </v>
       </c>
@@ -1226,8 +1302,12 @@
       <c r="I22" t="str">
         <v>2212JPI01S</v>
       </c>
-      <c r="J22" t="str">
-        <v>01.06.23 03.20.23 REV 1 01.15.24 REV 2 03.28.24 REV 3 04.02.24 REV 4 (W/ADD ALT 1 SIGNAGE)</v>
+      <c r="J22" t="str" xml:space="preserve">
+        <v xml:space="preserve">01.06.23 03.20.23 REV 1
+ 01.15.24 REV 2
+ 03.28.24 REV 3
+ 04.02.24 REV 4
+ (W/ADD ALT 1 SIGNAGE)</v>
       </c>
       <c r="K22" t="str">
         <v>JEFFERSON LOYD PARK PH 1.</v>
@@ -1236,7 +1316,7 @@
         <v>2212JPI01S Jefferson Loyd Park Ph. 1 Signage REV 4.xlsx</v>
       </c>
     </row>
-    <row r="23">
+    <row r="23" xml:space="preserve">
       <c r="A23" t="str">
         <v xml:space="preserve">#3: LEASING CENTER - INTERIOR SIGNAGE </v>
       </c>
@@ -1264,8 +1344,12 @@
       <c r="I23" t="str">
         <v>2212JPI01S</v>
       </c>
-      <c r="J23" t="str">
-        <v>01.06.23 03.20.23 REV 1 01.15.24 REV 2 03.28.24 REV 3 04.02.24 REV 4 (W/ADD ALT 1 SIGNAGE)</v>
+      <c r="J23" t="str" xml:space="preserve">
+        <v xml:space="preserve">01.06.23 03.20.23 REV 1
+ 01.15.24 REV 2
+ 03.28.24 REV 3
+ 04.02.24 REV 4
+ (W/ADD ALT 1 SIGNAGE)</v>
       </c>
       <c r="K23" t="str">
         <v>JEFFERSON LOYD PARK PH 1.</v>
@@ -1274,7 +1358,7 @@
         <v>2212JPI01S Jefferson Loyd Park Ph. 1 Signage REV 4.xlsx</v>
       </c>
     </row>
-    <row r="24">
+    <row r="24" xml:space="preserve">
       <c r="A24" t="str">
         <v xml:space="preserve">#3: LEASING CENTER - INTERIOR SIGNAGE </v>
       </c>
@@ -1302,8 +1386,12 @@
       <c r="I24" t="str">
         <v>2212JPI01S</v>
       </c>
-      <c r="J24" t="str">
-        <v>01.06.23 03.20.23 REV 1 01.15.24 REV 2 03.28.24 REV 3 04.02.24 REV 4 (W/ADD ALT 1 SIGNAGE)</v>
+      <c r="J24" t="str" xml:space="preserve">
+        <v xml:space="preserve">01.06.23 03.20.23 REV 1
+ 01.15.24 REV 2
+ 03.28.24 REV 3
+ 04.02.24 REV 4
+ (W/ADD ALT 1 SIGNAGE)</v>
       </c>
       <c r="K24" t="str">
         <v>JEFFERSON LOYD PARK PH 1.</v>
@@ -1312,7 +1400,7 @@
         <v>2212JPI01S Jefferson Loyd Park Ph. 1 Signage REV 4.xlsx</v>
       </c>
     </row>
-    <row r="25">
+    <row r="25" xml:space="preserve">
       <c r="A25" t="str">
         <v xml:space="preserve">#3: LEASING CENTER - INTERIOR  SIGNAGE  </v>
       </c>
@@ -1340,8 +1428,12 @@
       <c r="I25" t="str">
         <v>2212JPI01S</v>
       </c>
-      <c r="J25" t="str">
-        <v>01.06.23 03.20.23 REV 1 01.15.24 REV 2 03.28.24 REV 3 04.02.24 REV 4 (W/ADD ALT 1 SIGNAGE)</v>
+      <c r="J25" t="str" xml:space="preserve">
+        <v xml:space="preserve">01.06.23 03.20.23 REV 1
+ 01.15.24 REV 2
+ 03.28.24 REV 3
+ 04.02.24 REV 4
+ (W/ADD ALT 1 SIGNAGE)</v>
       </c>
       <c r="K25" t="str">
         <v>JEFFERSON LOYD PARK PH 1.</v>
@@ -1350,7 +1442,7 @@
         <v>2212JPI01S Jefferson Loyd Park Ph. 1 Signage REV 4.xlsx</v>
       </c>
     </row>
-    <row r="26">
+    <row r="26" xml:space="preserve">
       <c r="A26" t="str">
         <v xml:space="preserve">#3: LEASING CENTER - INTERIOR  SIGNAGE  </v>
       </c>
@@ -1378,8 +1470,12 @@
       <c r="I26" t="str">
         <v>2212JPI01S</v>
       </c>
-      <c r="J26" t="str">
-        <v>01.06.23 03.20.23 REV 1 01.15.24 REV 2 03.28.24 REV 3 04.02.24 REV 4 (W/ADD ALT 1 SIGNAGE)</v>
+      <c r="J26" t="str" xml:space="preserve">
+        <v xml:space="preserve">01.06.23 03.20.23 REV 1
+ 01.15.24 REV 2
+ 03.28.24 REV 3
+ 04.02.24 REV 4
+ (W/ADD ALT 1 SIGNAGE)</v>
       </c>
       <c r="K26" t="str">
         <v>JEFFERSON LOYD PARK PH 1.</v>
@@ -1388,7 +1484,7 @@
         <v>2212JPI01S Jefferson Loyd Park Ph. 1 Signage REV 4.xlsx</v>
       </c>
     </row>
-    <row r="27">
+    <row r="27" xml:space="preserve">
       <c r="A27" t="str">
         <v xml:space="preserve">#3: LEASING CENTER - INTERIOR  SIGNAGE  </v>
       </c>
@@ -1416,8 +1512,12 @@
       <c r="I27" t="str">
         <v>2212JPI01S</v>
       </c>
-      <c r="J27" t="str">
-        <v>01.06.23 03.20.23 REV 1 01.15.24 REV 2 03.28.24 REV 3 04.02.24 REV 4 (W/ADD ALT 1 SIGNAGE)</v>
+      <c r="J27" t="str" xml:space="preserve">
+        <v xml:space="preserve">01.06.23 03.20.23 REV 1
+ 01.15.24 REV 2
+ 03.28.24 REV 3
+ 04.02.24 REV 4
+ (W/ADD ALT 1 SIGNAGE)</v>
       </c>
       <c r="K27" t="str">
         <v>JEFFERSON LOYD PARK PH 1.</v>
@@ -1426,7 +1526,7 @@
         <v>2212JPI01S Jefferson Loyd Park Ph. 1 Signage REV 4.xlsx</v>
       </c>
     </row>
-    <row r="28">
+    <row r="28" xml:space="preserve">
       <c r="A28" t="str">
         <v xml:space="preserve">#3: LEASING CENTER - INTERIOR  SIGNAGE  </v>
       </c>
@@ -1454,8 +1554,12 @@
       <c r="I28" t="str">
         <v>2212JPI01S</v>
       </c>
-      <c r="J28" t="str">
-        <v>01.06.23 03.20.23 REV 1 01.15.24 REV 2 03.28.24 REV 3 04.02.24 REV 4 (W/ADD ALT 1 SIGNAGE)</v>
+      <c r="J28" t="str" xml:space="preserve">
+        <v xml:space="preserve">01.06.23 03.20.23 REV 1
+ 01.15.24 REV 2
+ 03.28.24 REV 3
+ 04.02.24 REV 4
+ (W/ADD ALT 1 SIGNAGE)</v>
       </c>
       <c r="K28" t="str">
         <v>JEFFERSON LOYD PARK PH 1.</v>
@@ -1464,7 +1568,7 @@
         <v>2212JPI01S Jefferson Loyd Park Ph. 1 Signage REV 4.xlsx</v>
       </c>
     </row>
-    <row r="29">
+    <row r="29" xml:space="preserve">
       <c r="A29" t="str">
         <v xml:space="preserve">#3: LEASING CENTER - INTERIOR  SIGNAGE  </v>
       </c>
@@ -1492,8 +1596,12 @@
       <c r="I29" t="str">
         <v>2212JPI01S</v>
       </c>
-      <c r="J29" t="str">
-        <v>01.06.23 03.20.23 REV 1 01.15.24 REV 2 03.28.24 REV 3 04.02.24 REV 4 (W/ADD ALT 1 SIGNAGE)</v>
+      <c r="J29" t="str" xml:space="preserve">
+        <v xml:space="preserve">01.06.23 03.20.23 REV 1
+ 01.15.24 REV 2
+ 03.28.24 REV 3
+ 04.02.24 REV 4
+ (W/ADD ALT 1 SIGNAGE)</v>
       </c>
       <c r="K29" t="str">
         <v>JEFFERSON LOYD PARK PH 1.</v>
@@ -1502,7 +1610,7 @@
         <v>2212JPI01S Jefferson Loyd Park Ph. 1 Signage REV 4.xlsx</v>
       </c>
     </row>
-    <row r="30">
+    <row r="30" xml:space="preserve">
       <c r="A30" t="str">
         <v xml:space="preserve">#4: SITE SIGNAGE  </v>
       </c>
@@ -1530,8 +1638,12 @@
       <c r="I30" t="str">
         <v>2212JPI01S</v>
       </c>
-      <c r="J30" t="str">
-        <v>01.06.23 03.20.23 REV 1 01.15.24 REV 2 03.28.24 REV 3 04.02.24 REV 4 (W/ADD ALT 1 SIGNAGE)</v>
+      <c r="J30" t="str" xml:space="preserve">
+        <v xml:space="preserve">01.06.23 03.20.23 REV 1
+ 01.15.24 REV 2
+ 03.28.24 REV 3
+ 04.02.24 REV 4
+ (W/ADD ALT 1 SIGNAGE)</v>
       </c>
       <c r="K30" t="str">
         <v>JEFFERSON LOYD PARK PH 1.</v>
@@ -1540,7 +1652,7 @@
         <v>2212JPI01S Jefferson Loyd Park Ph. 1 Signage REV 4.xlsx</v>
       </c>
     </row>
-    <row r="31">
+    <row r="31" xml:space="preserve">
       <c r="A31" t="str">
         <v xml:space="preserve">#4: SITE SIGNAGE  </v>
       </c>
@@ -1568,8 +1680,12 @@
       <c r="I31" t="str">
         <v>2212JPI01S</v>
       </c>
-      <c r="J31" t="str">
-        <v>01.06.23 03.20.23 REV 1 01.15.24 REV 2 03.28.24 REV 3 04.02.24 REV 4 (W/ADD ALT 1 SIGNAGE)</v>
+      <c r="J31" t="str" xml:space="preserve">
+        <v xml:space="preserve">01.06.23 03.20.23 REV 1
+ 01.15.24 REV 2
+ 03.28.24 REV 3
+ 04.02.24 REV 4
+ (W/ADD ALT 1 SIGNAGE)</v>
       </c>
       <c r="K31" t="str">
         <v>JEFFERSON LOYD PARK PH 1.</v>
@@ -1578,7 +1694,7 @@
         <v>2212JPI01S Jefferson Loyd Park Ph. 1 Signage REV 4.xlsx</v>
       </c>
     </row>
-    <row r="32">
+    <row r="32" xml:space="preserve">
       <c r="A32" t="str">
         <v xml:space="preserve">#4: SITE SIGNAGE  </v>
       </c>
@@ -1606,8 +1722,12 @@
       <c r="I32" t="str">
         <v>2212JPI01S</v>
       </c>
-      <c r="J32" t="str">
-        <v>01.06.23 03.20.23 REV 1 01.15.24 REV 2 03.28.24 REV 3 04.02.24 REV 4 (W/ADD ALT 1 SIGNAGE)</v>
+      <c r="J32" t="str" xml:space="preserve">
+        <v xml:space="preserve">01.06.23 03.20.23 REV 1
+ 01.15.24 REV 2
+ 03.28.24 REV 3
+ 04.02.24 REV 4
+ (W/ADD ALT 1 SIGNAGE)</v>
       </c>
       <c r="K32" t="str">
         <v>JEFFERSON LOYD PARK PH 1.</v>
@@ -1616,7 +1736,7 @@
         <v>2212JPI01S Jefferson Loyd Park Ph. 1 Signage REV 4.xlsx</v>
       </c>
     </row>
-    <row r="33">
+    <row r="33" xml:space="preserve">
       <c r="A33" t="str">
         <v xml:space="preserve">#4: SITE SIGNAGE  </v>
       </c>
@@ -1644,8 +1764,12 @@
       <c r="I33" t="str">
         <v>2212JPI01S</v>
       </c>
-      <c r="J33" t="str">
-        <v>01.06.23 03.20.23 REV 1 01.15.24 REV 2 03.28.24 REV 3 04.02.24 REV 4 (W/ADD ALT 1 SIGNAGE)</v>
+      <c r="J33" t="str" xml:space="preserve">
+        <v xml:space="preserve">01.06.23 03.20.23 REV 1
+ 01.15.24 REV 2
+ 03.28.24 REV 3
+ 04.02.24 REV 4
+ (W/ADD ALT 1 SIGNAGE)</v>
       </c>
       <c r="K33" t="str">
         <v>JEFFERSON LOYD PARK PH 1.</v>
@@ -1654,7 +1778,7 @@
         <v>2212JPI01S Jefferson Loyd Park Ph. 1 Signage REV 4.xlsx</v>
       </c>
     </row>
-    <row r="34">
+    <row r="34" xml:space="preserve">
       <c r="A34" t="str">
         <v xml:space="preserve">#4: SITE SIGNAGE  </v>
       </c>
@@ -1682,8 +1806,12 @@
       <c r="I34" t="str">
         <v>2212JPI01S</v>
       </c>
-      <c r="J34" t="str">
-        <v>01.06.23 03.20.23 REV 1 01.15.24 REV 2 03.28.24 REV 3 04.02.24 REV 4 (W/ADD ALT 1 SIGNAGE)</v>
+      <c r="J34" t="str" xml:space="preserve">
+        <v xml:space="preserve">01.06.23 03.20.23 REV 1
+ 01.15.24 REV 2
+ 03.28.24 REV 3
+ 04.02.24 REV 4
+ (W/ADD ALT 1 SIGNAGE)</v>
       </c>
       <c r="K34" t="str">
         <v>JEFFERSON LOYD PARK PH 1.</v>
@@ -1692,7 +1820,7 @@
         <v>2212JPI01S Jefferson Loyd Park Ph. 1 Signage REV 4.xlsx</v>
       </c>
     </row>
-    <row r="35">
+    <row r="35" xml:space="preserve">
       <c r="A35" t="str">
         <v xml:space="preserve">#4: SITE SIGNAGE  </v>
       </c>
@@ -1720,8 +1848,12 @@
       <c r="I35" t="str">
         <v>2212JPI01S</v>
       </c>
-      <c r="J35" t="str">
-        <v>01.06.23 03.20.23 REV 1 01.15.24 REV 2 03.28.24 REV 3 04.02.24 REV 4 (W/ADD ALT 1 SIGNAGE)</v>
+      <c r="J35" t="str" xml:space="preserve">
+        <v xml:space="preserve">01.06.23 03.20.23 REV 1
+ 01.15.24 REV 2
+ 03.28.24 REV 3
+ 04.02.24 REV 4
+ (W/ADD ALT 1 SIGNAGE)</v>
       </c>
       <c r="K35" t="str">
         <v>JEFFERSON LOYD PARK PH 1.</v>
@@ -1730,7 +1862,7 @@
         <v>2212JPI01S Jefferson Loyd Park Ph. 1 Signage REV 4.xlsx</v>
       </c>
     </row>
-    <row r="36">
+    <row r="36" xml:space="preserve">
       <c r="A36" t="str">
         <v xml:space="preserve">#4: SITE SIGNAGE  </v>
       </c>
@@ -1758,8 +1890,12 @@
       <c r="I36" t="str">
         <v>2212JPI01S</v>
       </c>
-      <c r="J36" t="str">
-        <v>01.06.23 03.20.23 REV 1 01.15.24 REV 2 03.28.24 REV 3 04.02.24 REV 4 (W/ADD ALT 1 SIGNAGE)</v>
+      <c r="J36" t="str" xml:space="preserve">
+        <v xml:space="preserve">01.06.23 03.20.23 REV 1
+ 01.15.24 REV 2
+ 03.28.24 REV 3
+ 04.02.24 REV 4
+ (W/ADD ALT 1 SIGNAGE)</v>
       </c>
       <c r="K36" t="str">
         <v>JEFFERSON LOYD PARK PH 1.</v>
@@ -1768,7 +1904,7 @@
         <v>2212JPI01S Jefferson Loyd Park Ph. 1 Signage REV 4.xlsx</v>
       </c>
     </row>
-    <row r="37">
+    <row r="37" xml:space="preserve">
       <c r="A37" t="str">
         <v xml:space="preserve">#4: SITE SIGNAGE  </v>
       </c>
@@ -1796,8 +1932,12 @@
       <c r="I37" t="str">
         <v>2212JPI01S</v>
       </c>
-      <c r="J37" t="str">
-        <v>01.06.23 03.20.23 REV 1 01.15.24 REV 2 03.28.24 REV 3 04.02.24 REV 4 (W/ADD ALT 1 SIGNAGE)</v>
+      <c r="J37" t="str" xml:space="preserve">
+        <v xml:space="preserve">01.06.23 03.20.23 REV 1
+ 01.15.24 REV 2
+ 03.28.24 REV 3
+ 04.02.24 REV 4
+ (W/ADD ALT 1 SIGNAGE)</v>
       </c>
       <c r="K37" t="str">
         <v>JEFFERSON LOYD PARK PH 1.</v>
@@ -1806,7 +1946,7 @@
         <v>2212JPI01S Jefferson Loyd Park Ph. 1 Signage REV 4.xlsx</v>
       </c>
     </row>
-    <row r="38">
+    <row r="38" xml:space="preserve">
       <c r="A38" t="str">
         <v xml:space="preserve">#5: BUILDING #2 (TYPE II) SIGNAGE </v>
       </c>
@@ -1834,8 +1974,12 @@
       <c r="I38" t="str">
         <v>2212JPI01S</v>
       </c>
-      <c r="J38" t="str">
-        <v>01.06.23 03.20.23 REV 1 01.15.24 REV 2 03.28.24 REV 3 04.02.24 REV 4 (W/ADD ALT 1 SIGNAGE)</v>
+      <c r="J38" t="str" xml:space="preserve">
+        <v xml:space="preserve">01.06.23 03.20.23 REV 1
+ 01.15.24 REV 2
+ 03.28.24 REV 3
+ 04.02.24 REV 4
+ (W/ADD ALT 1 SIGNAGE)</v>
       </c>
       <c r="K38" t="str">
         <v>JEFFERSON LOYD PARK PH 1.</v>
@@ -1844,7 +1988,7 @@
         <v>2212JPI01S Jefferson Loyd Park Ph. 1 Signage REV 4.xlsx</v>
       </c>
     </row>
-    <row r="39">
+    <row r="39" xml:space="preserve">
       <c r="A39" t="str">
         <v xml:space="preserve">#5: BUILDING #2 (TYPE II) SIGNAGE </v>
       </c>
@@ -1872,8 +2016,12 @@
       <c r="I39" t="str">
         <v>2212JPI01S</v>
       </c>
-      <c r="J39" t="str">
-        <v>01.06.23 03.20.23 REV 1 01.15.24 REV 2 03.28.24 REV 3 04.02.24 REV 4 (W/ADD ALT 1 SIGNAGE)</v>
+      <c r="J39" t="str" xml:space="preserve">
+        <v xml:space="preserve">01.06.23 03.20.23 REV 1
+ 01.15.24 REV 2
+ 03.28.24 REV 3
+ 04.02.24 REV 4
+ (W/ADD ALT 1 SIGNAGE)</v>
       </c>
       <c r="K39" t="str">
         <v>JEFFERSON LOYD PARK PH 1.</v>
@@ -1882,7 +2030,7 @@
         <v>2212JPI01S Jefferson Loyd Park Ph. 1 Signage REV 4.xlsx</v>
       </c>
     </row>
-    <row r="40">
+    <row r="40" xml:space="preserve">
       <c r="A40" t="str">
         <v xml:space="preserve">#5: BUILDING #2 (TYPE II) SIGNAGE </v>
       </c>
@@ -1910,8 +2058,12 @@
       <c r="I40" t="str">
         <v>2212JPI01S</v>
       </c>
-      <c r="J40" t="str">
-        <v>01.06.23 03.20.23 REV 1 01.15.24 REV 2 03.28.24 REV 3 04.02.24 REV 4 (W/ADD ALT 1 SIGNAGE)</v>
+      <c r="J40" t="str" xml:space="preserve">
+        <v xml:space="preserve">01.06.23 03.20.23 REV 1
+ 01.15.24 REV 2
+ 03.28.24 REV 3
+ 04.02.24 REV 4
+ (W/ADD ALT 1 SIGNAGE)</v>
       </c>
       <c r="K40" t="str">
         <v>JEFFERSON LOYD PARK PH 1.</v>
@@ -1920,7 +2072,7 @@
         <v>2212JPI01S Jefferson Loyd Park Ph. 1 Signage REV 4.xlsx</v>
       </c>
     </row>
-    <row r="41">
+    <row r="41" xml:space="preserve">
       <c r="A41" t="str">
         <v xml:space="preserve">#5: BUILDING #2 (TYPE II) SIGNAGE </v>
       </c>
@@ -1948,8 +2100,12 @@
       <c r="I41" t="str">
         <v>2212JPI01S</v>
       </c>
-      <c r="J41" t="str">
-        <v>01.06.23 03.20.23 REV 1 01.15.24 REV 2 03.28.24 REV 3 04.02.24 REV 4 (W/ADD ALT 1 SIGNAGE)</v>
+      <c r="J41" t="str" xml:space="preserve">
+        <v xml:space="preserve">01.06.23 03.20.23 REV 1
+ 01.15.24 REV 2
+ 03.28.24 REV 3
+ 04.02.24 REV 4
+ (W/ADD ALT 1 SIGNAGE)</v>
       </c>
       <c r="K41" t="str">
         <v>JEFFERSON LOYD PARK PH 1.</v>
@@ -1958,7 +2114,7 @@
         <v>2212JPI01S Jefferson Loyd Park Ph. 1 Signage REV 4.xlsx</v>
       </c>
     </row>
-    <row r="42">
+    <row r="42" xml:space="preserve">
       <c r="A42" t="str">
         <v xml:space="preserve">#5: BUILDING #2 (TYPE II) SIGNAGE </v>
       </c>
@@ -1986,8 +2142,12 @@
       <c r="I42" t="str">
         <v>2212JPI01S</v>
       </c>
-      <c r="J42" t="str">
-        <v>01.06.23 03.20.23 REV 1 01.15.24 REV 2 03.28.24 REV 3 04.02.24 REV 4 (W/ADD ALT 1 SIGNAGE)</v>
+      <c r="J42" t="str" xml:space="preserve">
+        <v xml:space="preserve">01.06.23 03.20.23 REV 1
+ 01.15.24 REV 2
+ 03.28.24 REV 3
+ 04.02.24 REV 4
+ (W/ADD ALT 1 SIGNAGE)</v>
       </c>
       <c r="K42" t="str">
         <v>JEFFERSON LOYD PARK PH 1.</v>
@@ -1996,7 +2156,7 @@
         <v>2212JPI01S Jefferson Loyd Park Ph. 1 Signage REV 4.xlsx</v>
       </c>
     </row>
-    <row r="43">
+    <row r="43" xml:space="preserve">
       <c r="A43" t="str">
         <v xml:space="preserve">#5: BUILDING #2 (TYPE II) SIGNAGE </v>
       </c>
@@ -2024,8 +2184,12 @@
       <c r="I43" t="str">
         <v>2212JPI01S</v>
       </c>
-      <c r="J43" t="str">
-        <v>01.06.23 03.20.23 REV 1 01.15.24 REV 2 03.28.24 REV 3 04.02.24 REV 4 (W/ADD ALT 1 SIGNAGE)</v>
+      <c r="J43" t="str" xml:space="preserve">
+        <v xml:space="preserve">01.06.23 03.20.23 REV 1
+ 01.15.24 REV 2
+ 03.28.24 REV 3
+ 04.02.24 REV 4
+ (W/ADD ALT 1 SIGNAGE)</v>
       </c>
       <c r="K43" t="str">
         <v>JEFFERSON LOYD PARK PH 1.</v>
@@ -2034,7 +2198,7 @@
         <v>2212JPI01S Jefferson Loyd Park Ph. 1 Signage REV 4.xlsx</v>
       </c>
     </row>
-    <row r="44">
+    <row r="44" xml:space="preserve">
       <c r="A44" t="str">
         <v xml:space="preserve">#5: BUILDING #2 (TYPE II) SIGNAGE </v>
       </c>
@@ -2062,8 +2226,12 @@
       <c r="I44" t="str">
         <v>2212JPI01S</v>
       </c>
-      <c r="J44" t="str">
-        <v>01.06.23 03.20.23 REV 1 01.15.24 REV 2 03.28.24 REV 3 04.02.24 REV 4 (W/ADD ALT 1 SIGNAGE)</v>
+      <c r="J44" t="str" xml:space="preserve">
+        <v xml:space="preserve">01.06.23 03.20.23 REV 1
+ 01.15.24 REV 2
+ 03.28.24 REV 3
+ 04.02.24 REV 4
+ (W/ADD ALT 1 SIGNAGE)</v>
       </c>
       <c r="K44" t="str">
         <v>JEFFERSON LOYD PARK PH 1.</v>
@@ -2072,7 +2240,7 @@
         <v>2212JPI01S Jefferson Loyd Park Ph. 1 Signage REV 4.xlsx</v>
       </c>
     </row>
-    <row r="45">
+    <row r="45" xml:space="preserve">
       <c r="A45" t="str">
         <v xml:space="preserve">#5: BUILDING #2 (TYPE II) SIGNAGE </v>
       </c>
@@ -2100,8 +2268,12 @@
       <c r="I45" t="str">
         <v>2212JPI01S</v>
       </c>
-      <c r="J45" t="str">
-        <v>01.06.23 03.20.23 REV 1 01.15.24 REV 2 03.28.24 REV 3 04.02.24 REV 4 (W/ADD ALT 1 SIGNAGE)</v>
+      <c r="J45" t="str" xml:space="preserve">
+        <v xml:space="preserve">01.06.23 03.20.23 REV 1
+ 01.15.24 REV 2
+ 03.28.24 REV 3
+ 04.02.24 REV 4
+ (W/ADD ALT 1 SIGNAGE)</v>
       </c>
       <c r="K45" t="str">
         <v>JEFFERSON LOYD PARK PH 1.</v>
@@ -2110,7 +2282,7 @@
         <v>2212JPI01S Jefferson Loyd Park Ph. 1 Signage REV 4.xlsx</v>
       </c>
     </row>
-    <row r="46">
+    <row r="46" xml:space="preserve">
       <c r="A46" t="str">
         <v xml:space="preserve">#5: BUILDING #2 (TYPE II) SIGNAGE </v>
       </c>
@@ -2138,8 +2310,12 @@
       <c r="I46" t="str">
         <v>2212JPI01S</v>
       </c>
-      <c r="J46" t="str">
-        <v>01.06.23 03.20.23 REV 1 01.15.24 REV 2 03.28.24 REV 3 04.02.24 REV 4 (W/ADD ALT 1 SIGNAGE)</v>
+      <c r="J46" t="str" xml:space="preserve">
+        <v xml:space="preserve">01.06.23 03.20.23 REV 1
+ 01.15.24 REV 2
+ 03.28.24 REV 3
+ 04.02.24 REV 4
+ (W/ADD ALT 1 SIGNAGE)</v>
       </c>
       <c r="K46" t="str">
         <v>JEFFERSON LOYD PARK PH 1.</v>
@@ -2148,7 +2324,7 @@
         <v>2212JPI01S Jefferson Loyd Park Ph. 1 Signage REV 4.xlsx</v>
       </c>
     </row>
-    <row r="47">
+    <row r="47" xml:space="preserve">
       <c r="A47" t="str">
         <v xml:space="preserve">#5: BUILDING #2 (TYPE II) SIGNAGE </v>
       </c>
@@ -2176,8 +2352,12 @@
       <c r="I47" t="str">
         <v>2212JPI01S</v>
       </c>
-      <c r="J47" t="str">
-        <v>01.06.23 03.20.23 REV 1 01.15.24 REV 2 03.28.24 REV 3 04.02.24 REV 4 (W/ADD ALT 1 SIGNAGE)</v>
+      <c r="J47" t="str" xml:space="preserve">
+        <v xml:space="preserve">01.06.23 03.20.23 REV 1
+ 01.15.24 REV 2
+ 03.28.24 REV 3
+ 04.02.24 REV 4
+ (W/ADD ALT 1 SIGNAGE)</v>
       </c>
       <c r="K47" t="str">
         <v>JEFFERSON LOYD PARK PH 1.</v>
@@ -2186,7 +2366,7 @@
         <v>2212JPI01S Jefferson Loyd Park Ph. 1 Signage REV 4.xlsx</v>
       </c>
     </row>
-    <row r="48">
+    <row r="48" xml:space="preserve">
       <c r="A48" t="str">
         <v xml:space="preserve">#5: BUILDING #2 (TYPE II) SIGNAGE </v>
       </c>
@@ -2214,8 +2394,12 @@
       <c r="I48" t="str">
         <v>2212JPI01S</v>
       </c>
-      <c r="J48" t="str">
-        <v>01.06.23 03.20.23 REV 1 01.15.24 REV 2 03.28.24 REV 3 04.02.24 REV 4 (W/ADD ALT 1 SIGNAGE)</v>
+      <c r="J48" t="str" xml:space="preserve">
+        <v xml:space="preserve">01.06.23 03.20.23 REV 1
+ 01.15.24 REV 2
+ 03.28.24 REV 3
+ 04.02.24 REV 4
+ (W/ADD ALT 1 SIGNAGE)</v>
       </c>
       <c r="K48" t="str">
         <v>JEFFERSON LOYD PARK PH 1.</v>
@@ -2224,7 +2408,7 @@
         <v>2212JPI01S Jefferson Loyd Park Ph. 1 Signage REV 4.xlsx</v>
       </c>
     </row>
-    <row r="49">
+    <row r="49" xml:space="preserve">
       <c r="A49" t="str">
         <v xml:space="preserve">#5: BUILDING #2 (TYPE II) SIGNAGE </v>
       </c>
@@ -2252,8 +2436,12 @@
       <c r="I49" t="str">
         <v>2212JPI01S</v>
       </c>
-      <c r="J49" t="str">
-        <v>01.06.23 03.20.23 REV 1 01.15.24 REV 2 03.28.24 REV 3 04.02.24 REV 4 (W/ADD ALT 1 SIGNAGE)</v>
+      <c r="J49" t="str" xml:space="preserve">
+        <v xml:space="preserve">01.06.23 03.20.23 REV 1
+ 01.15.24 REV 2
+ 03.28.24 REV 3
+ 04.02.24 REV 4
+ (W/ADD ALT 1 SIGNAGE)</v>
       </c>
       <c r="K49" t="str">
         <v>JEFFERSON LOYD PARK PH 1.</v>
@@ -2262,7 +2450,7 @@
         <v>2212JPI01S Jefferson Loyd Park Ph. 1 Signage REV 4.xlsx</v>
       </c>
     </row>
-    <row r="50">
+    <row r="50" xml:space="preserve">
       <c r="A50" t="str">
         <v xml:space="preserve">#6: BUILDING #3 (TYPE I) SIGNAGE </v>
       </c>
@@ -2290,8 +2478,12 @@
       <c r="I50" t="str">
         <v>2212JPI01S</v>
       </c>
-      <c r="J50" t="str">
-        <v>01.06.23 03.20.23 REV 1 01.15.24 REV 2 03.28.24 REV 3 04.02.24 REV 4 (W/ADD ALT 1 SIGNAGE)</v>
+      <c r="J50" t="str" xml:space="preserve">
+        <v xml:space="preserve">01.06.23 03.20.23 REV 1
+ 01.15.24 REV 2
+ 03.28.24 REV 3
+ 04.02.24 REV 4
+ (W/ADD ALT 1 SIGNAGE)</v>
       </c>
       <c r="K50" t="str">
         <v>JEFFERSON LOYD PARK PH 1.</v>
@@ -2300,7 +2492,7 @@
         <v>2212JPI01S Jefferson Loyd Park Ph. 1 Signage REV 4.xlsx</v>
       </c>
     </row>
-    <row r="51">
+    <row r="51" xml:space="preserve">
       <c r="A51" t="str">
         <v xml:space="preserve">#6: BUILDING #3 (TYPE I) SIGNAGE </v>
       </c>
@@ -2328,8 +2520,12 @@
       <c r="I51" t="str">
         <v>2212JPI01S</v>
       </c>
-      <c r="J51" t="str">
-        <v>01.06.23 03.20.23 REV 1 01.15.24 REV 2 03.28.24 REV 3 04.02.24 REV 4 (W/ADD ALT 1 SIGNAGE)</v>
+      <c r="J51" t="str" xml:space="preserve">
+        <v xml:space="preserve">01.06.23 03.20.23 REV 1
+ 01.15.24 REV 2
+ 03.28.24 REV 3
+ 04.02.24 REV 4
+ (W/ADD ALT 1 SIGNAGE)</v>
       </c>
       <c r="K51" t="str">
         <v>JEFFERSON LOYD PARK PH 1.</v>
@@ -2338,7 +2534,7 @@
         <v>2212JPI01S Jefferson Loyd Park Ph. 1 Signage REV 4.xlsx</v>
       </c>
     </row>
-    <row r="52">
+    <row r="52" xml:space="preserve">
       <c r="A52" t="str">
         <v xml:space="preserve">#6: BUILDING #3 (TYPE I) SIGNAGE </v>
       </c>
@@ -2366,8 +2562,12 @@
       <c r="I52" t="str">
         <v>2212JPI01S</v>
       </c>
-      <c r="J52" t="str">
-        <v>01.06.23 03.20.23 REV 1 01.15.24 REV 2 03.28.24 REV 3 04.02.24 REV 4 (W/ADD ALT 1 SIGNAGE)</v>
+      <c r="J52" t="str" xml:space="preserve">
+        <v xml:space="preserve">01.06.23 03.20.23 REV 1
+ 01.15.24 REV 2
+ 03.28.24 REV 3
+ 04.02.24 REV 4
+ (W/ADD ALT 1 SIGNAGE)</v>
       </c>
       <c r="K52" t="str">
         <v>JEFFERSON LOYD PARK PH 1.</v>
@@ -2376,7 +2576,7 @@
         <v>2212JPI01S Jefferson Loyd Park Ph. 1 Signage REV 4.xlsx</v>
       </c>
     </row>
-    <row r="53">
+    <row r="53" xml:space="preserve">
       <c r="A53" t="str">
         <v xml:space="preserve">#6: BUILDING #3 (TYPE I) SIGNAGE </v>
       </c>
@@ -2404,8 +2604,12 @@
       <c r="I53" t="str">
         <v>2212JPI01S</v>
       </c>
-      <c r="J53" t="str">
-        <v>01.06.23 03.20.23 REV 1 01.15.24 REV 2 03.28.24 REV 3 04.02.24 REV 4 (W/ADD ALT 1 SIGNAGE)</v>
+      <c r="J53" t="str" xml:space="preserve">
+        <v xml:space="preserve">01.06.23 03.20.23 REV 1
+ 01.15.24 REV 2
+ 03.28.24 REV 3
+ 04.02.24 REV 4
+ (W/ADD ALT 1 SIGNAGE)</v>
       </c>
       <c r="K53" t="str">
         <v>JEFFERSON LOYD PARK PH 1.</v>
@@ -2414,7 +2618,7 @@
         <v>2212JPI01S Jefferson Loyd Park Ph. 1 Signage REV 4.xlsx</v>
       </c>
     </row>
-    <row r="54">
+    <row r="54" xml:space="preserve">
       <c r="A54" t="str">
         <v xml:space="preserve">#6: BUILDING #3 (TYPE I) SIGNAGE </v>
       </c>
@@ -2442,8 +2646,12 @@
       <c r="I54" t="str">
         <v>2212JPI01S</v>
       </c>
-      <c r="J54" t="str">
-        <v>01.06.23 03.20.23 REV 1 01.15.24 REV 2 03.28.24 REV 3 04.02.24 REV 4 (W/ADD ALT 1 SIGNAGE)</v>
+      <c r="J54" t="str" xml:space="preserve">
+        <v xml:space="preserve">01.06.23 03.20.23 REV 1
+ 01.15.24 REV 2
+ 03.28.24 REV 3
+ 04.02.24 REV 4
+ (W/ADD ALT 1 SIGNAGE)</v>
       </c>
       <c r="K54" t="str">
         <v>JEFFERSON LOYD PARK PH 1.</v>
@@ -2452,7 +2660,7 @@
         <v>2212JPI01S Jefferson Loyd Park Ph. 1 Signage REV 4.xlsx</v>
       </c>
     </row>
-    <row r="55">
+    <row r="55" xml:space="preserve">
       <c r="A55" t="str">
         <v xml:space="preserve">#6: BUILDING #3 (TYPE I) SIGNAGE </v>
       </c>
@@ -2480,8 +2688,12 @@
       <c r="I55" t="str">
         <v>2212JPI01S</v>
       </c>
-      <c r="J55" t="str">
-        <v>01.06.23 03.20.23 REV 1 01.15.24 REV 2 03.28.24 REV 3 04.02.24 REV 4 (W/ADD ALT 1 SIGNAGE)</v>
+      <c r="J55" t="str" xml:space="preserve">
+        <v xml:space="preserve">01.06.23 03.20.23 REV 1
+ 01.15.24 REV 2
+ 03.28.24 REV 3
+ 04.02.24 REV 4
+ (W/ADD ALT 1 SIGNAGE)</v>
       </c>
       <c r="K55" t="str">
         <v>JEFFERSON LOYD PARK PH 1.</v>
@@ -2490,7 +2702,7 @@
         <v>2212JPI01S Jefferson Loyd Park Ph. 1 Signage REV 4.xlsx</v>
       </c>
     </row>
-    <row r="56">
+    <row r="56" xml:space="preserve">
       <c r="A56" t="str">
         <v xml:space="preserve">#6: BUILDING #3 (TYPE I) SIGNAGE </v>
       </c>
@@ -2518,8 +2730,12 @@
       <c r="I56" t="str">
         <v>2212JPI01S</v>
       </c>
-      <c r="J56" t="str">
-        <v>01.06.23 03.20.23 REV 1 01.15.24 REV 2 03.28.24 REV 3 04.02.24 REV 4 (W/ADD ALT 1 SIGNAGE)</v>
+      <c r="J56" t="str" xml:space="preserve">
+        <v xml:space="preserve">01.06.23 03.20.23 REV 1
+ 01.15.24 REV 2
+ 03.28.24 REV 3
+ 04.02.24 REV 4
+ (W/ADD ALT 1 SIGNAGE)</v>
       </c>
       <c r="K56" t="str">
         <v>JEFFERSON LOYD PARK PH 1.</v>
@@ -2528,7 +2744,7 @@
         <v>2212JPI01S Jefferson Loyd Park Ph. 1 Signage REV 4.xlsx</v>
       </c>
     </row>
-    <row r="57">
+    <row r="57" xml:space="preserve">
       <c r="A57" t="str">
         <v xml:space="preserve">#6: BUILDING #3 (TYPE I) SIGNAGE </v>
       </c>
@@ -2556,8 +2772,12 @@
       <c r="I57" t="str">
         <v>2212JPI01S</v>
       </c>
-      <c r="J57" t="str">
-        <v>01.06.23 03.20.23 REV 1 01.15.24 REV 2 03.28.24 REV 3 04.02.24 REV 4 (W/ADD ALT 1 SIGNAGE)</v>
+      <c r="J57" t="str" xml:space="preserve">
+        <v xml:space="preserve">01.06.23 03.20.23 REV 1
+ 01.15.24 REV 2
+ 03.28.24 REV 3
+ 04.02.24 REV 4
+ (W/ADD ALT 1 SIGNAGE)</v>
       </c>
       <c r="K57" t="str">
         <v>JEFFERSON LOYD PARK PH 1.</v>
@@ -2566,7 +2786,7 @@
         <v>2212JPI01S Jefferson Loyd Park Ph. 1 Signage REV 4.xlsx</v>
       </c>
     </row>
-    <row r="58">
+    <row r="58" xml:space="preserve">
       <c r="A58" t="str">
         <v xml:space="preserve">#6: BUILDING #3 (TYPE I) SIGNAGE </v>
       </c>
@@ -2594,8 +2814,12 @@
       <c r="I58" t="str">
         <v>2212JPI01S</v>
       </c>
-      <c r="J58" t="str">
-        <v>01.06.23 03.20.23 REV 1 01.15.24 REV 2 03.28.24 REV 3 04.02.24 REV 4 (W/ADD ALT 1 SIGNAGE)</v>
+      <c r="J58" t="str" xml:space="preserve">
+        <v xml:space="preserve">01.06.23 03.20.23 REV 1
+ 01.15.24 REV 2
+ 03.28.24 REV 3
+ 04.02.24 REV 4
+ (W/ADD ALT 1 SIGNAGE)</v>
       </c>
       <c r="K58" t="str">
         <v>JEFFERSON LOYD PARK PH 1.</v>
@@ -2604,7 +2828,7 @@
         <v>2212JPI01S Jefferson Loyd Park Ph. 1 Signage REV 4.xlsx</v>
       </c>
     </row>
-    <row r="59">
+    <row r="59" xml:space="preserve">
       <c r="A59" t="str">
         <v xml:space="preserve">#6: BUILDING #3 (TYPE I) SIGNAGE </v>
       </c>
@@ -2632,8 +2856,12 @@
       <c r="I59" t="str">
         <v>2212JPI01S</v>
       </c>
-      <c r="J59" t="str">
-        <v>01.06.23 03.20.23 REV 1 01.15.24 REV 2 03.28.24 REV 3 04.02.24 REV 4 (W/ADD ALT 1 SIGNAGE)</v>
+      <c r="J59" t="str" xml:space="preserve">
+        <v xml:space="preserve">01.06.23 03.20.23 REV 1
+ 01.15.24 REV 2
+ 03.28.24 REV 3
+ 04.02.24 REV 4
+ (W/ADD ALT 1 SIGNAGE)</v>
       </c>
       <c r="K59" t="str">
         <v>JEFFERSON LOYD PARK PH 1.</v>
@@ -2642,7 +2870,7 @@
         <v>2212JPI01S Jefferson Loyd Park Ph. 1 Signage REV 4.xlsx</v>
       </c>
     </row>
-    <row r="60">
+    <row r="60" xml:space="preserve">
       <c r="A60" t="str">
         <v xml:space="preserve">#7: BUILDING #4 (TYPE 1) SIGNAGE </v>
       </c>
@@ -2670,8 +2898,12 @@
       <c r="I60" t="str">
         <v>2212JPI01S</v>
       </c>
-      <c r="J60" t="str">
-        <v>01.06.23 03.20.23 REV 1 01.15.24 REV 2 03.28.24 REV 3 04.02.24 REV 4 (W/ADD ALT 1 SIGNAGE)</v>
+      <c r="J60" t="str" xml:space="preserve">
+        <v xml:space="preserve">01.06.23 03.20.23 REV 1
+ 01.15.24 REV 2
+ 03.28.24 REV 3
+ 04.02.24 REV 4
+ (W/ADD ALT 1 SIGNAGE)</v>
       </c>
       <c r="K60" t="str">
         <v>JEFFERSON LOYD PARK PH 1.</v>
@@ -2680,7 +2912,7 @@
         <v>2212JPI01S Jefferson Loyd Park Ph. 1 Signage REV 4.xlsx</v>
       </c>
     </row>
-    <row r="61">
+    <row r="61" xml:space="preserve">
       <c r="A61" t="str">
         <v xml:space="preserve">#7: BUILDING #4 (TYPE 1) SIGNAGE </v>
       </c>
@@ -2708,8 +2940,12 @@
       <c r="I61" t="str">
         <v>2212JPI01S</v>
       </c>
-      <c r="J61" t="str">
-        <v>01.06.23 03.20.23 REV 1 01.15.24 REV 2 03.28.24 REV 3 04.02.24 REV 4 (W/ADD ALT 1 SIGNAGE)</v>
+      <c r="J61" t="str" xml:space="preserve">
+        <v xml:space="preserve">01.06.23 03.20.23 REV 1
+ 01.15.24 REV 2
+ 03.28.24 REV 3
+ 04.02.24 REV 4
+ (W/ADD ALT 1 SIGNAGE)</v>
       </c>
       <c r="K61" t="str">
         <v>JEFFERSON LOYD PARK PH 1.</v>
@@ -2718,7 +2954,7 @@
         <v>2212JPI01S Jefferson Loyd Park Ph. 1 Signage REV 4.xlsx</v>
       </c>
     </row>
-    <row r="62">
+    <row r="62" xml:space="preserve">
       <c r="A62" t="str">
         <v xml:space="preserve">#7: BUILDING #4 (TYPE 1) SIGNAGE </v>
       </c>
@@ -2746,8 +2982,12 @@
       <c r="I62" t="str">
         <v>2212JPI01S</v>
       </c>
-      <c r="J62" t="str">
-        <v>01.06.23 03.20.23 REV 1 01.15.24 REV 2 03.28.24 REV 3 04.02.24 REV 4 (W/ADD ALT 1 SIGNAGE)</v>
+      <c r="J62" t="str" xml:space="preserve">
+        <v xml:space="preserve">01.06.23 03.20.23 REV 1
+ 01.15.24 REV 2
+ 03.28.24 REV 3
+ 04.02.24 REV 4
+ (W/ADD ALT 1 SIGNAGE)</v>
       </c>
       <c r="K62" t="str">
         <v>JEFFERSON LOYD PARK PH 1.</v>
@@ -2756,7 +2996,7 @@
         <v>2212JPI01S Jefferson Loyd Park Ph. 1 Signage REV 4.xlsx</v>
       </c>
     </row>
-    <row r="63">
+    <row r="63" xml:space="preserve">
       <c r="A63" t="str">
         <v xml:space="preserve">#7: BUILDING #4 (TYPE 1) SIGNAGE </v>
       </c>
@@ -2784,8 +3024,12 @@
       <c r="I63" t="str">
         <v>2212JPI01S</v>
       </c>
-      <c r="J63" t="str">
-        <v>01.06.23 03.20.23 REV 1 01.15.24 REV 2 03.28.24 REV 3 04.02.24 REV 4 (W/ADD ALT 1 SIGNAGE)</v>
+      <c r="J63" t="str" xml:space="preserve">
+        <v xml:space="preserve">01.06.23 03.20.23 REV 1
+ 01.15.24 REV 2
+ 03.28.24 REV 3
+ 04.02.24 REV 4
+ (W/ADD ALT 1 SIGNAGE)</v>
       </c>
       <c r="K63" t="str">
         <v>JEFFERSON LOYD PARK PH 1.</v>
@@ -2794,7 +3038,7 @@
         <v>2212JPI01S Jefferson Loyd Park Ph. 1 Signage REV 4.xlsx</v>
       </c>
     </row>
-    <row r="64">
+    <row r="64" xml:space="preserve">
       <c r="A64" t="str">
         <v xml:space="preserve">#7: BUILDING #4 (TYPE 1) SIGNAGE </v>
       </c>
@@ -2822,8 +3066,12 @@
       <c r="I64" t="str">
         <v>2212JPI01S</v>
       </c>
-      <c r="J64" t="str">
-        <v>01.06.23 03.20.23 REV 1 01.15.24 REV 2 03.28.24 REV 3 04.02.24 REV 4 (W/ADD ALT 1 SIGNAGE)</v>
+      <c r="J64" t="str" xml:space="preserve">
+        <v xml:space="preserve">01.06.23 03.20.23 REV 1
+ 01.15.24 REV 2
+ 03.28.24 REV 3
+ 04.02.24 REV 4
+ (W/ADD ALT 1 SIGNAGE)</v>
       </c>
       <c r="K64" t="str">
         <v>JEFFERSON LOYD PARK PH 1.</v>
@@ -2832,7 +3080,7 @@
         <v>2212JPI01S Jefferson Loyd Park Ph. 1 Signage REV 4.xlsx</v>
       </c>
     </row>
-    <row r="65">
+    <row r="65" xml:space="preserve">
       <c r="A65" t="str">
         <v xml:space="preserve">#7: BUILDING #4 (TYPE 1) SIGNAGE </v>
       </c>
@@ -2860,8 +3108,12 @@
       <c r="I65" t="str">
         <v>2212JPI01S</v>
       </c>
-      <c r="J65" t="str">
-        <v>01.06.23 03.20.23 REV 1 01.15.24 REV 2 03.28.24 REV 3 04.02.24 REV 4 (W/ADD ALT 1 SIGNAGE)</v>
+      <c r="J65" t="str" xml:space="preserve">
+        <v xml:space="preserve">01.06.23 03.20.23 REV 1
+ 01.15.24 REV 2
+ 03.28.24 REV 3
+ 04.02.24 REV 4
+ (W/ADD ALT 1 SIGNAGE)</v>
       </c>
       <c r="K65" t="str">
         <v>JEFFERSON LOYD PARK PH 1.</v>
@@ -2870,7 +3122,7 @@
         <v>2212JPI01S Jefferson Loyd Park Ph. 1 Signage REV 4.xlsx</v>
       </c>
     </row>
-    <row r="66">
+    <row r="66" xml:space="preserve">
       <c r="A66" t="str">
         <v xml:space="preserve">#7: BUILDING #4 (TYPE 1) SIGNAGE </v>
       </c>
@@ -2898,8 +3150,12 @@
       <c r="I66" t="str">
         <v>2212JPI01S</v>
       </c>
-      <c r="J66" t="str">
-        <v>01.06.23 03.20.23 REV 1 01.15.24 REV 2 03.28.24 REV 3 04.02.24 REV 4 (W/ADD ALT 1 SIGNAGE)</v>
+      <c r="J66" t="str" xml:space="preserve">
+        <v xml:space="preserve">01.06.23 03.20.23 REV 1
+ 01.15.24 REV 2
+ 03.28.24 REV 3
+ 04.02.24 REV 4
+ (W/ADD ALT 1 SIGNAGE)</v>
       </c>
       <c r="K66" t="str">
         <v>JEFFERSON LOYD PARK PH 1.</v>
@@ -2908,7 +3164,7 @@
         <v>2212JPI01S Jefferson Loyd Park Ph. 1 Signage REV 4.xlsx</v>
       </c>
     </row>
-    <row r="67">
+    <row r="67" xml:space="preserve">
       <c r="A67" t="str">
         <v xml:space="preserve">#7: BUILDING #4 (TYPE 1) SIGNAGE </v>
       </c>
@@ -2936,8 +3192,12 @@
       <c r="I67" t="str">
         <v>2212JPI01S</v>
       </c>
-      <c r="J67" t="str">
-        <v>01.06.23 03.20.23 REV 1 01.15.24 REV 2 03.28.24 REV 3 04.02.24 REV 4 (W/ADD ALT 1 SIGNAGE)</v>
+      <c r="J67" t="str" xml:space="preserve">
+        <v xml:space="preserve">01.06.23 03.20.23 REV 1
+ 01.15.24 REV 2
+ 03.28.24 REV 3
+ 04.02.24 REV 4
+ (W/ADD ALT 1 SIGNAGE)</v>
       </c>
       <c r="K67" t="str">
         <v>JEFFERSON LOYD PARK PH 1.</v>
@@ -2946,7 +3206,7 @@
         <v>2212JPI01S Jefferson Loyd Park Ph. 1 Signage REV 4.xlsx</v>
       </c>
     </row>
-    <row r="68">
+    <row r="68" xml:space="preserve">
       <c r="A68" t="str">
         <v xml:space="preserve">#7: BUILDING #4 (TYPE 1) SIGNAGE </v>
       </c>
@@ -2974,8 +3234,12 @@
       <c r="I68" t="str">
         <v>2212JPI01S</v>
       </c>
-      <c r="J68" t="str">
-        <v>01.06.23 03.20.23 REV 1 01.15.24 REV 2 03.28.24 REV 3 04.02.24 REV 4 (W/ADD ALT 1 SIGNAGE)</v>
+      <c r="J68" t="str" xml:space="preserve">
+        <v xml:space="preserve">01.06.23 03.20.23 REV 1
+ 01.15.24 REV 2
+ 03.28.24 REV 3
+ 04.02.24 REV 4
+ (W/ADD ALT 1 SIGNAGE)</v>
       </c>
       <c r="K68" t="str">
         <v>JEFFERSON LOYD PARK PH 1.</v>
@@ -2984,7 +3248,7 @@
         <v>2212JPI01S Jefferson Loyd Park Ph. 1 Signage REV 4.xlsx</v>
       </c>
     </row>
-    <row r="69">
+    <row r="69" xml:space="preserve">
       <c r="A69" t="str">
         <v xml:space="preserve">#7: BUILDING #4 (TYPE 1) SIGNAGE </v>
       </c>
@@ -3012,8 +3276,12 @@
       <c r="I69" t="str">
         <v>2212JPI01S</v>
       </c>
-      <c r="J69" t="str">
-        <v>01.06.23 03.20.23 REV 1 01.15.24 REV 2 03.28.24 REV 3 04.02.24 REV 4 (W/ADD ALT 1 SIGNAGE)</v>
+      <c r="J69" t="str" xml:space="preserve">
+        <v xml:space="preserve">01.06.23 03.20.23 REV 1
+ 01.15.24 REV 2
+ 03.28.24 REV 3
+ 04.02.24 REV 4
+ (W/ADD ALT 1 SIGNAGE)</v>
       </c>
       <c r="K69" t="str">
         <v>JEFFERSON LOYD PARK PH 1.</v>
@@ -3022,7 +3290,7 @@
         <v>2212JPI01S Jefferson Loyd Park Ph. 1 Signage REV 4.xlsx</v>
       </c>
     </row>
-    <row r="70">
+    <row r="70" xml:space="preserve">
       <c r="A70" t="str">
         <v xml:space="preserve">#8: BUILDING #5 (TYPE II) SIGNAGE </v>
       </c>
@@ -3050,8 +3318,12 @@
       <c r="I70" t="str">
         <v>2212JPI01S</v>
       </c>
-      <c r="J70" t="str">
-        <v>01.06.23 03.20.23 REV 1 01.15.24 REV 2 03.28.24 REV 3 04.02.24 REV 4 (W/ADD ALT 1 SIGNAGE)</v>
+      <c r="J70" t="str" xml:space="preserve">
+        <v xml:space="preserve">01.06.23 03.20.23 REV 1
+ 01.15.24 REV 2
+ 03.28.24 REV 3
+ 04.02.24 REV 4
+ (W/ADD ALT 1 SIGNAGE)</v>
       </c>
       <c r="K70" t="str">
         <v>JEFFERSON LOYD PARK PH 1.</v>
@@ -3060,7 +3332,7 @@
         <v>2212JPI01S Jefferson Loyd Park Ph. 1 Signage REV 4.xlsx</v>
       </c>
     </row>
-    <row r="71">
+    <row r="71" xml:space="preserve">
       <c r="A71" t="str">
         <v xml:space="preserve">#8: BUILDING #5 (TYPE II) SIGNAGE </v>
       </c>
@@ -3088,8 +3360,12 @@
       <c r="I71" t="str">
         <v>2212JPI01S</v>
       </c>
-      <c r="J71" t="str">
-        <v>01.06.23 03.20.23 REV 1 01.15.24 REV 2 03.28.24 REV 3 04.02.24 REV 4 (W/ADD ALT 1 SIGNAGE)</v>
+      <c r="J71" t="str" xml:space="preserve">
+        <v xml:space="preserve">01.06.23 03.20.23 REV 1
+ 01.15.24 REV 2
+ 03.28.24 REV 3
+ 04.02.24 REV 4
+ (W/ADD ALT 1 SIGNAGE)</v>
       </c>
       <c r="K71" t="str">
         <v>JEFFERSON LOYD PARK PH 1.</v>
@@ -3098,7 +3374,7 @@
         <v>2212JPI01S Jefferson Loyd Park Ph. 1 Signage REV 4.xlsx</v>
       </c>
     </row>
-    <row r="72">
+    <row r="72" xml:space="preserve">
       <c r="A72" t="str">
         <v xml:space="preserve">#8: BUILDING #5 (TYPE II) SIGNAGE </v>
       </c>
@@ -3126,8 +3402,12 @@
       <c r="I72" t="str">
         <v>2212JPI01S</v>
       </c>
-      <c r="J72" t="str">
-        <v>01.06.23 03.20.23 REV 1 01.15.24 REV 2 03.28.24 REV 3 04.02.24 REV 4 (W/ADD ALT 1 SIGNAGE)</v>
+      <c r="J72" t="str" xml:space="preserve">
+        <v xml:space="preserve">01.06.23 03.20.23 REV 1
+ 01.15.24 REV 2
+ 03.28.24 REV 3
+ 04.02.24 REV 4
+ (W/ADD ALT 1 SIGNAGE)</v>
       </c>
       <c r="K72" t="str">
         <v>JEFFERSON LOYD PARK PH 1.</v>
@@ -3136,7 +3416,7 @@
         <v>2212JPI01S Jefferson Loyd Park Ph. 1 Signage REV 4.xlsx</v>
       </c>
     </row>
-    <row r="73">
+    <row r="73" xml:space="preserve">
       <c r="A73" t="str">
         <v xml:space="preserve">#8: BUILDING #5 (TYPE II) SIGNAGE </v>
       </c>
@@ -3164,8 +3444,12 @@
       <c r="I73" t="str">
         <v>2212JPI01S</v>
       </c>
-      <c r="J73" t="str">
-        <v>01.06.23 03.20.23 REV 1 01.15.24 REV 2 03.28.24 REV 3 04.02.24 REV 4 (W/ADD ALT 1 SIGNAGE)</v>
+      <c r="J73" t="str" xml:space="preserve">
+        <v xml:space="preserve">01.06.23 03.20.23 REV 1
+ 01.15.24 REV 2
+ 03.28.24 REV 3
+ 04.02.24 REV 4
+ (W/ADD ALT 1 SIGNAGE)</v>
       </c>
       <c r="K73" t="str">
         <v>JEFFERSON LOYD PARK PH 1.</v>
@@ -3174,7 +3458,7 @@
         <v>2212JPI01S Jefferson Loyd Park Ph. 1 Signage REV 4.xlsx</v>
       </c>
     </row>
-    <row r="74">
+    <row r="74" xml:space="preserve">
       <c r="A74" t="str">
         <v xml:space="preserve">#8: BUILDING #5 (TYPE II) SIGNAGE </v>
       </c>
@@ -3202,8 +3486,12 @@
       <c r="I74" t="str">
         <v>2212JPI01S</v>
       </c>
-      <c r="J74" t="str">
-        <v>01.06.23 03.20.23 REV 1 01.15.24 REV 2 03.28.24 REV 3 04.02.24 REV 4 (W/ADD ALT 1 SIGNAGE)</v>
+      <c r="J74" t="str" xml:space="preserve">
+        <v xml:space="preserve">01.06.23 03.20.23 REV 1
+ 01.15.24 REV 2
+ 03.28.24 REV 3
+ 04.02.24 REV 4
+ (W/ADD ALT 1 SIGNAGE)</v>
       </c>
       <c r="K74" t="str">
         <v>JEFFERSON LOYD PARK PH 1.</v>
@@ -3212,7 +3500,7 @@
         <v>2212JPI01S Jefferson Loyd Park Ph. 1 Signage REV 4.xlsx</v>
       </c>
     </row>
-    <row r="75">
+    <row r="75" xml:space="preserve">
       <c r="A75" t="str">
         <v xml:space="preserve">#8: BUILDING #5 (TYPE II) SIGNAGE </v>
       </c>
@@ -3240,8 +3528,12 @@
       <c r="I75" t="str">
         <v>2212JPI01S</v>
       </c>
-      <c r="J75" t="str">
-        <v>01.06.23 03.20.23 REV 1 01.15.24 REV 2 03.28.24 REV 3 04.02.24 REV 4 (W/ADD ALT 1 SIGNAGE)</v>
+      <c r="J75" t="str" xml:space="preserve">
+        <v xml:space="preserve">01.06.23 03.20.23 REV 1
+ 01.15.24 REV 2
+ 03.28.24 REV 3
+ 04.02.24 REV 4
+ (W/ADD ALT 1 SIGNAGE)</v>
       </c>
       <c r="K75" t="str">
         <v>JEFFERSON LOYD PARK PH 1.</v>
@@ -3250,7 +3542,7 @@
         <v>2212JPI01S Jefferson Loyd Park Ph. 1 Signage REV 4.xlsx</v>
       </c>
     </row>
-    <row r="76">
+    <row r="76" xml:space="preserve">
       <c r="A76" t="str">
         <v xml:space="preserve">#8: BUILDING #5 (TYPE II) SIGNAGE </v>
       </c>
@@ -3278,8 +3570,12 @@
       <c r="I76" t="str">
         <v>2212JPI01S</v>
       </c>
-      <c r="J76" t="str">
-        <v>01.06.23 03.20.23 REV 1 01.15.24 REV 2 03.28.24 REV 3 04.02.24 REV 4 (W/ADD ALT 1 SIGNAGE)</v>
+      <c r="J76" t="str" xml:space="preserve">
+        <v xml:space="preserve">01.06.23 03.20.23 REV 1
+ 01.15.24 REV 2
+ 03.28.24 REV 3
+ 04.02.24 REV 4
+ (W/ADD ALT 1 SIGNAGE)</v>
       </c>
       <c r="K76" t="str">
         <v>JEFFERSON LOYD PARK PH 1.</v>
@@ -3288,7 +3584,7 @@
         <v>2212JPI01S Jefferson Loyd Park Ph. 1 Signage REV 4.xlsx</v>
       </c>
     </row>
-    <row r="77">
+    <row r="77" xml:space="preserve">
       <c r="A77" t="str">
         <v xml:space="preserve">#8: BUILDING #5 (TYPE II) SIGNAGE </v>
       </c>
@@ -3316,8 +3612,12 @@
       <c r="I77" t="str">
         <v>2212JPI01S</v>
       </c>
-      <c r="J77" t="str">
-        <v>01.06.23 03.20.23 REV 1 01.15.24 REV 2 03.28.24 REV 3 04.02.24 REV 4 (W/ADD ALT 1 SIGNAGE)</v>
+      <c r="J77" t="str" xml:space="preserve">
+        <v xml:space="preserve">01.06.23 03.20.23 REV 1
+ 01.15.24 REV 2
+ 03.28.24 REV 3
+ 04.02.24 REV 4
+ (W/ADD ALT 1 SIGNAGE)</v>
       </c>
       <c r="K77" t="str">
         <v>JEFFERSON LOYD PARK PH 1.</v>
@@ -3326,7 +3626,7 @@
         <v>2212JPI01S Jefferson Loyd Park Ph. 1 Signage REV 4.xlsx</v>
       </c>
     </row>
-    <row r="78">
+    <row r="78" xml:space="preserve">
       <c r="A78" t="str">
         <v xml:space="preserve">#8: BUILDING #5 (TYPE II) SIGNAGE </v>
       </c>
@@ -3354,8 +3654,12 @@
       <c r="I78" t="str">
         <v>2212JPI01S</v>
       </c>
-      <c r="J78" t="str">
-        <v>01.06.23 03.20.23 REV 1 01.15.24 REV 2 03.28.24 REV 3 04.02.24 REV 4 (W/ADD ALT 1 SIGNAGE)</v>
+      <c r="J78" t="str" xml:space="preserve">
+        <v xml:space="preserve">01.06.23 03.20.23 REV 1
+ 01.15.24 REV 2
+ 03.28.24 REV 3
+ 04.02.24 REV 4
+ (W/ADD ALT 1 SIGNAGE)</v>
       </c>
       <c r="K78" t="str">
         <v>JEFFERSON LOYD PARK PH 1.</v>
@@ -3364,7 +3668,7 @@
         <v>2212JPI01S Jefferson Loyd Park Ph. 1 Signage REV 4.xlsx</v>
       </c>
     </row>
-    <row r="79">
+    <row r="79" xml:space="preserve">
       <c r="A79" t="str">
         <v xml:space="preserve">#8: BUILDING #5 (TYPE II) SIGNAGE </v>
       </c>
@@ -3392,8 +3696,12 @@
       <c r="I79" t="str">
         <v>2212JPI01S</v>
       </c>
-      <c r="J79" t="str">
-        <v>01.06.23 03.20.23 REV 1 01.15.24 REV 2 03.28.24 REV 3 04.02.24 REV 4 (W/ADD ALT 1 SIGNAGE)</v>
+      <c r="J79" t="str" xml:space="preserve">
+        <v xml:space="preserve">01.06.23 03.20.23 REV 1
+ 01.15.24 REV 2
+ 03.28.24 REV 3
+ 04.02.24 REV 4
+ (W/ADD ALT 1 SIGNAGE)</v>
       </c>
       <c r="K79" t="str">
         <v>JEFFERSON LOYD PARK PH 1.</v>
@@ -3402,7 +3710,7 @@
         <v>2212JPI01S Jefferson Loyd Park Ph. 1 Signage REV 4.xlsx</v>
       </c>
     </row>
-    <row r="80">
+    <row r="80" xml:space="preserve">
       <c r="A80" t="str">
         <v xml:space="preserve">#8: BUILDING #5 (TYPE II) SIGNAGE </v>
       </c>
@@ -3430,8 +3738,12 @@
       <c r="I80" t="str">
         <v>2212JPI01S</v>
       </c>
-      <c r="J80" t="str">
-        <v>01.06.23 03.20.23 REV 1 01.15.24 REV 2 03.28.24 REV 3 04.02.24 REV 4 (W/ADD ALT 1 SIGNAGE)</v>
+      <c r="J80" t="str" xml:space="preserve">
+        <v xml:space="preserve">01.06.23 03.20.23 REV 1
+ 01.15.24 REV 2
+ 03.28.24 REV 3
+ 04.02.24 REV 4
+ (W/ADD ALT 1 SIGNAGE)</v>
       </c>
       <c r="K80" t="str">
         <v>JEFFERSON LOYD PARK PH 1.</v>
@@ -3440,7 +3752,7 @@
         <v>2212JPI01S Jefferson Loyd Park Ph. 1 Signage REV 4.xlsx</v>
       </c>
     </row>
-    <row r="81">
+    <row r="81" xml:space="preserve">
       <c r="A81" t="str">
         <v xml:space="preserve">#8: BUILDING #5 (TYPE II) SIGNAGE </v>
       </c>
@@ -3468,8 +3780,12 @@
       <c r="I81" t="str">
         <v>2212JPI01S</v>
       </c>
-      <c r="J81" t="str">
-        <v>01.06.23 03.20.23 REV 1 01.15.24 REV 2 03.28.24 REV 3 04.02.24 REV 4 (W/ADD ALT 1 SIGNAGE)</v>
+      <c r="J81" t="str" xml:space="preserve">
+        <v xml:space="preserve">01.06.23 03.20.23 REV 1
+ 01.15.24 REV 2
+ 03.28.24 REV 3
+ 04.02.24 REV 4
+ (W/ADD ALT 1 SIGNAGE)</v>
       </c>
       <c r="K81" t="str">
         <v>JEFFERSON LOYD PARK PH 1.</v>
@@ -3478,7 +3794,7 @@
         <v>2212JPI01S Jefferson Loyd Park Ph. 1 Signage REV 4.xlsx</v>
       </c>
     </row>
-    <row r="82">
+    <row r="82" xml:space="preserve">
       <c r="A82" t="str">
         <v xml:space="preserve">#9: BUILDING #6 (TYPE IV) SIGNAGE </v>
       </c>
@@ -3506,8 +3822,12 @@
       <c r="I82" t="str">
         <v>2212JPI01S</v>
       </c>
-      <c r="J82" t="str">
-        <v>01.06.23 03.20.23 REV 1 01.15.24 REV 2 03.28.24 REV 3 04.02.24 REV 4 (W/ADD ALT 1 SIGNAGE)</v>
+      <c r="J82" t="str" xml:space="preserve">
+        <v xml:space="preserve">01.06.23 03.20.23 REV 1
+ 01.15.24 REV 2
+ 03.28.24 REV 3
+ 04.02.24 REV 4
+ (W/ADD ALT 1 SIGNAGE)</v>
       </c>
       <c r="K82" t="str">
         <v>JEFFERSON LOYD PARK PH 1.</v>
@@ -3516,7 +3836,7 @@
         <v>2212JPI01S Jefferson Loyd Park Ph. 1 Signage REV 4.xlsx</v>
       </c>
     </row>
-    <row r="83">
+    <row r="83" xml:space="preserve">
       <c r="A83" t="str">
         <v xml:space="preserve">#9: BUILDING #6 (TYPE IV) SIGNAGE </v>
       </c>
@@ -3544,8 +3864,12 @@
       <c r="I83" t="str">
         <v>2212JPI01S</v>
       </c>
-      <c r="J83" t="str">
-        <v>01.06.23 03.20.23 REV 1 01.15.24 REV 2 03.28.24 REV 3 04.02.24 REV 4 (W/ADD ALT 1 SIGNAGE)</v>
+      <c r="J83" t="str" xml:space="preserve">
+        <v xml:space="preserve">01.06.23 03.20.23 REV 1
+ 01.15.24 REV 2
+ 03.28.24 REV 3
+ 04.02.24 REV 4
+ (W/ADD ALT 1 SIGNAGE)</v>
       </c>
       <c r="K83" t="str">
         <v>JEFFERSON LOYD PARK PH 1.</v>
@@ -3554,7 +3878,7 @@
         <v>2212JPI01S Jefferson Loyd Park Ph. 1 Signage REV 4.xlsx</v>
       </c>
     </row>
-    <row r="84">
+    <row r="84" xml:space="preserve">
       <c r="A84" t="str">
         <v xml:space="preserve">#9: BUILDING #6 (TYPE IV) SIGNAGE </v>
       </c>
@@ -3582,8 +3906,12 @@
       <c r="I84" t="str">
         <v>2212JPI01S</v>
       </c>
-      <c r="J84" t="str">
-        <v>01.06.23 03.20.23 REV 1 01.15.24 REV 2 03.28.24 REV 3 04.02.24 REV 4 (W/ADD ALT 1 SIGNAGE)</v>
+      <c r="J84" t="str" xml:space="preserve">
+        <v xml:space="preserve">01.06.23 03.20.23 REV 1
+ 01.15.24 REV 2
+ 03.28.24 REV 3
+ 04.02.24 REV 4
+ (W/ADD ALT 1 SIGNAGE)</v>
       </c>
       <c r="K84" t="str">
         <v>JEFFERSON LOYD PARK PH 1.</v>
@@ -3592,7 +3920,7 @@
         <v>2212JPI01S Jefferson Loyd Park Ph. 1 Signage REV 4.xlsx</v>
       </c>
     </row>
-    <row r="85">
+    <row r="85" xml:space="preserve">
       <c r="A85" t="str">
         <v xml:space="preserve">#9: BUILDING #6 (TYPE IV) SIGNAGE </v>
       </c>
@@ -3620,8 +3948,12 @@
       <c r="I85" t="str">
         <v>2212JPI01S</v>
       </c>
-      <c r="J85" t="str">
-        <v>01.06.23 03.20.23 REV 1 01.15.24 REV 2 03.28.24 REV 3 04.02.24 REV 4 (W/ADD ALT 1 SIGNAGE)</v>
+      <c r="J85" t="str" xml:space="preserve">
+        <v xml:space="preserve">01.06.23 03.20.23 REV 1
+ 01.15.24 REV 2
+ 03.28.24 REV 3
+ 04.02.24 REV 4
+ (W/ADD ALT 1 SIGNAGE)</v>
       </c>
       <c r="K85" t="str">
         <v>JEFFERSON LOYD PARK PH 1.</v>
@@ -3630,7 +3962,7 @@
         <v>2212JPI01S Jefferson Loyd Park Ph. 1 Signage REV 4.xlsx</v>
       </c>
     </row>
-    <row r="86">
+    <row r="86" xml:space="preserve">
       <c r="A86" t="str">
         <v xml:space="preserve">#9: BUILDING #6 (TYPE IV) SIGNAGE </v>
       </c>
@@ -3658,8 +3990,12 @@
       <c r="I86" t="str">
         <v>2212JPI01S</v>
       </c>
-      <c r="J86" t="str">
-        <v>01.06.23 03.20.23 REV 1 01.15.24 REV 2 03.28.24 REV 3 04.02.24 REV 4 (W/ADD ALT 1 SIGNAGE)</v>
+      <c r="J86" t="str" xml:space="preserve">
+        <v xml:space="preserve">01.06.23 03.20.23 REV 1
+ 01.15.24 REV 2
+ 03.28.24 REV 3
+ 04.02.24 REV 4
+ (W/ADD ALT 1 SIGNAGE)</v>
       </c>
       <c r="K86" t="str">
         <v>JEFFERSON LOYD PARK PH 1.</v>
@@ -3668,7 +4004,7 @@
         <v>2212JPI01S Jefferson Loyd Park Ph. 1 Signage REV 4.xlsx</v>
       </c>
     </row>
-    <row r="87">
+    <row r="87" xml:space="preserve">
       <c r="A87" t="str">
         <v xml:space="preserve">#9: BUILDING #6 (TYPE IV) SIGNAGE </v>
       </c>
@@ -3696,8 +4032,12 @@
       <c r="I87" t="str">
         <v>2212JPI01S</v>
       </c>
-      <c r="J87" t="str">
-        <v>01.06.23 03.20.23 REV 1 01.15.24 REV 2 03.28.24 REV 3 04.02.24 REV 4 (W/ADD ALT 1 SIGNAGE)</v>
+      <c r="J87" t="str" xml:space="preserve">
+        <v xml:space="preserve">01.06.23 03.20.23 REV 1
+ 01.15.24 REV 2
+ 03.28.24 REV 3
+ 04.02.24 REV 4
+ (W/ADD ALT 1 SIGNAGE)</v>
       </c>
       <c r="K87" t="str">
         <v>JEFFERSON LOYD PARK PH 1.</v>
@@ -3706,7 +4046,7 @@
         <v>2212JPI01S Jefferson Loyd Park Ph. 1 Signage REV 4.xlsx</v>
       </c>
     </row>
-    <row r="88">
+    <row r="88" xml:space="preserve">
       <c r="A88" t="str">
         <v xml:space="preserve">#9: BUILDING #6 (TYPE IV) SIGNAGE </v>
       </c>
@@ -3734,8 +4074,12 @@
       <c r="I88" t="str">
         <v>2212JPI01S</v>
       </c>
-      <c r="J88" t="str">
-        <v>01.06.23 03.20.23 REV 1 01.15.24 REV 2 03.28.24 REV 3 04.02.24 REV 4 (W/ADD ALT 1 SIGNAGE)</v>
+      <c r="J88" t="str" xml:space="preserve">
+        <v xml:space="preserve">01.06.23 03.20.23 REV 1
+ 01.15.24 REV 2
+ 03.28.24 REV 3
+ 04.02.24 REV 4
+ (W/ADD ALT 1 SIGNAGE)</v>
       </c>
       <c r="K88" t="str">
         <v>JEFFERSON LOYD PARK PH 1.</v>
@@ -3744,7 +4088,7 @@
         <v>2212JPI01S Jefferson Loyd Park Ph. 1 Signage REV 4.xlsx</v>
       </c>
     </row>
-    <row r="89">
+    <row r="89" xml:space="preserve">
       <c r="A89" t="str">
         <v xml:space="preserve">#9: BUILDING #6 (TYPE IV) SIGNAGE </v>
       </c>
@@ -3772,8 +4116,12 @@
       <c r="I89" t="str">
         <v>2212JPI01S</v>
       </c>
-      <c r="J89" t="str">
-        <v>01.06.23 03.20.23 REV 1 01.15.24 REV 2 03.28.24 REV 3 04.02.24 REV 4 (W/ADD ALT 1 SIGNAGE)</v>
+      <c r="J89" t="str" xml:space="preserve">
+        <v xml:space="preserve">01.06.23 03.20.23 REV 1
+ 01.15.24 REV 2
+ 03.28.24 REV 3
+ 04.02.24 REV 4
+ (W/ADD ALT 1 SIGNAGE)</v>
       </c>
       <c r="K89" t="str">
         <v>JEFFERSON LOYD PARK PH 1.</v>
@@ -3782,7 +4130,7 @@
         <v>2212JPI01S Jefferson Loyd Park Ph. 1 Signage REV 4.xlsx</v>
       </c>
     </row>
-    <row r="90">
+    <row r="90" xml:space="preserve">
       <c r="A90" t="str">
         <v xml:space="preserve">#9: BUILDING #6 (TYPE IV) SIGNAGE </v>
       </c>
@@ -3810,8 +4158,12 @@
       <c r="I90" t="str">
         <v>2212JPI01S</v>
       </c>
-      <c r="J90" t="str">
-        <v>01.06.23 03.20.23 REV 1 01.15.24 REV 2 03.28.24 REV 3 04.02.24 REV 4 (W/ADD ALT 1 SIGNAGE)</v>
+      <c r="J90" t="str" xml:space="preserve">
+        <v xml:space="preserve">01.06.23 03.20.23 REV 1
+ 01.15.24 REV 2
+ 03.28.24 REV 3
+ 04.02.24 REV 4
+ (W/ADD ALT 1 SIGNAGE)</v>
       </c>
       <c r="K90" t="str">
         <v>JEFFERSON LOYD PARK PH 1.</v>
@@ -3820,7 +4172,7 @@
         <v>2212JPI01S Jefferson Loyd Park Ph. 1 Signage REV 4.xlsx</v>
       </c>
     </row>
-    <row r="91">
+    <row r="91" xml:space="preserve">
       <c r="A91" t="str">
         <v xml:space="preserve">#9: BUILDING #6 (TYPE IV) SIGNAGE </v>
       </c>
@@ -3848,8 +4200,12 @@
       <c r="I91" t="str">
         <v>2212JPI01S</v>
       </c>
-      <c r="J91" t="str">
-        <v>01.06.23 03.20.23 REV 1 01.15.24 REV 2 03.28.24 REV 3 04.02.24 REV 4 (W/ADD ALT 1 SIGNAGE)</v>
+      <c r="J91" t="str" xml:space="preserve">
+        <v xml:space="preserve">01.06.23 03.20.23 REV 1
+ 01.15.24 REV 2
+ 03.28.24 REV 3
+ 04.02.24 REV 4
+ (W/ADD ALT 1 SIGNAGE)</v>
       </c>
       <c r="K91" t="str">
         <v>JEFFERSON LOYD PARK PH 1.</v>
@@ -3858,7 +4214,7 @@
         <v>2212JPI01S Jefferson Loyd Park Ph. 1 Signage REV 4.xlsx</v>
       </c>
     </row>
-    <row r="92">
+    <row r="92" xml:space="preserve">
       <c r="A92" t="str">
         <v xml:space="preserve">#9: BUILDING #6 (TYPE IV) SIGNAGE </v>
       </c>
@@ -3886,8 +4242,12 @@
       <c r="I92" t="str">
         <v>2212JPI01S</v>
       </c>
-      <c r="J92" t="str">
-        <v>01.06.23 03.20.23 REV 1 01.15.24 REV 2 03.28.24 REV 3 04.02.24 REV 4 (W/ADD ALT 1 SIGNAGE)</v>
+      <c r="J92" t="str" xml:space="preserve">
+        <v xml:space="preserve">01.06.23 03.20.23 REV 1
+ 01.15.24 REV 2
+ 03.28.24 REV 3
+ 04.02.24 REV 4
+ (W/ADD ALT 1 SIGNAGE)</v>
       </c>
       <c r="K92" t="str">
         <v>JEFFERSON LOYD PARK PH 1.</v>
@@ -3896,7 +4256,7 @@
         <v>2212JPI01S Jefferson Loyd Park Ph. 1 Signage REV 4.xlsx</v>
       </c>
     </row>
-    <row r="93">
+    <row r="93" xml:space="preserve">
       <c r="A93" t="str">
         <v xml:space="preserve">#10: BUILDING #7 (TYPE III) SIGNAGE </v>
       </c>
@@ -3924,8 +4284,12 @@
       <c r="I93" t="str">
         <v>2212JPI01S</v>
       </c>
-      <c r="J93" t="str">
-        <v>01.06.23 03.20.23 REV 1 01.15.24 REV 2 03.28.24 REV 3 04.02.24 REV 4 (W/ADD ALT 1 SIGNAGE)</v>
+      <c r="J93" t="str" xml:space="preserve">
+        <v xml:space="preserve">01.06.23 03.20.23 REV 1
+ 01.15.24 REV 2
+ 03.28.24 REV 3
+ 04.02.24 REV 4
+ (W/ADD ALT 1 SIGNAGE)</v>
       </c>
       <c r="K93" t="str">
         <v>JEFFERSON LOYD PARK PH 1.</v>
@@ -3934,7 +4298,7 @@
         <v>2212JPI01S Jefferson Loyd Park Ph. 1 Signage REV 4.xlsx</v>
       </c>
     </row>
-    <row r="94">
+    <row r="94" xml:space="preserve">
       <c r="A94" t="str">
         <v xml:space="preserve">#10: BUILDING #7 (TYPE III) SIGNAGE </v>
       </c>
@@ -3962,8 +4326,12 @@
       <c r="I94" t="str">
         <v>2212JPI01S</v>
       </c>
-      <c r="J94" t="str">
-        <v>01.06.23 03.20.23 REV 1 01.15.24 REV 2 03.28.24 REV 3 04.02.24 REV 4 (W/ADD ALT 1 SIGNAGE)</v>
+      <c r="J94" t="str" xml:space="preserve">
+        <v xml:space="preserve">01.06.23 03.20.23 REV 1
+ 01.15.24 REV 2
+ 03.28.24 REV 3
+ 04.02.24 REV 4
+ (W/ADD ALT 1 SIGNAGE)</v>
       </c>
       <c r="K94" t="str">
         <v>JEFFERSON LOYD PARK PH 1.</v>
@@ -3972,7 +4340,7 @@
         <v>2212JPI01S Jefferson Loyd Park Ph. 1 Signage REV 4.xlsx</v>
       </c>
     </row>
-    <row r="95">
+    <row r="95" xml:space="preserve">
       <c r="A95" t="str">
         <v xml:space="preserve">#10: BUILDING #7 (TYPE III) SIGNAGE </v>
       </c>
@@ -4000,8 +4368,12 @@
       <c r="I95" t="str">
         <v>2212JPI01S</v>
       </c>
-      <c r="J95" t="str">
-        <v>01.06.23 03.20.23 REV 1 01.15.24 REV 2 03.28.24 REV 3 04.02.24 REV 4 (W/ADD ALT 1 SIGNAGE)</v>
+      <c r="J95" t="str" xml:space="preserve">
+        <v xml:space="preserve">01.06.23 03.20.23 REV 1
+ 01.15.24 REV 2
+ 03.28.24 REV 3
+ 04.02.24 REV 4
+ (W/ADD ALT 1 SIGNAGE)</v>
       </c>
       <c r="K95" t="str">
         <v>JEFFERSON LOYD PARK PH 1.</v>
@@ -4010,7 +4382,7 @@
         <v>2212JPI01S Jefferson Loyd Park Ph. 1 Signage REV 4.xlsx</v>
       </c>
     </row>
-    <row r="96">
+    <row r="96" xml:space="preserve">
       <c r="A96" t="str">
         <v xml:space="preserve">#10: BUILDING #7 (TYPE III) SIGNAGE </v>
       </c>
@@ -4038,8 +4410,12 @@
       <c r="I96" t="str">
         <v>2212JPI01S</v>
       </c>
-      <c r="J96" t="str">
-        <v>01.06.23 03.20.23 REV 1 01.15.24 REV 2 03.28.24 REV 3 04.02.24 REV 4 (W/ADD ALT 1 SIGNAGE)</v>
+      <c r="J96" t="str" xml:space="preserve">
+        <v xml:space="preserve">01.06.23 03.20.23 REV 1
+ 01.15.24 REV 2
+ 03.28.24 REV 3
+ 04.02.24 REV 4
+ (W/ADD ALT 1 SIGNAGE)</v>
       </c>
       <c r="K96" t="str">
         <v>JEFFERSON LOYD PARK PH 1.</v>
@@ -4048,7 +4424,7 @@
         <v>2212JPI01S Jefferson Loyd Park Ph. 1 Signage REV 4.xlsx</v>
       </c>
     </row>
-    <row r="97">
+    <row r="97" xml:space="preserve">
       <c r="A97" t="str">
         <v xml:space="preserve">#10: BUILDING #7 (TYPE III) SIGNAGE </v>
       </c>
@@ -4076,8 +4452,12 @@
       <c r="I97" t="str">
         <v>2212JPI01S</v>
       </c>
-      <c r="J97" t="str">
-        <v>01.06.23 03.20.23 REV 1 01.15.24 REV 2 03.28.24 REV 3 04.02.24 REV 4 (W/ADD ALT 1 SIGNAGE)</v>
+      <c r="J97" t="str" xml:space="preserve">
+        <v xml:space="preserve">01.06.23 03.20.23 REV 1
+ 01.15.24 REV 2
+ 03.28.24 REV 3
+ 04.02.24 REV 4
+ (W/ADD ALT 1 SIGNAGE)</v>
       </c>
       <c r="K97" t="str">
         <v>JEFFERSON LOYD PARK PH 1.</v>
@@ -4086,7 +4466,7 @@
         <v>2212JPI01S Jefferson Loyd Park Ph. 1 Signage REV 4.xlsx</v>
       </c>
     </row>
-    <row r="98">
+    <row r="98" xml:space="preserve">
       <c r="A98" t="str">
         <v xml:space="preserve">#10: BUILDING #7 (TYPE III) SIGNAGE </v>
       </c>
@@ -4114,8 +4494,12 @@
       <c r="I98" t="str">
         <v>2212JPI01S</v>
       </c>
-      <c r="J98" t="str">
-        <v>01.06.23 03.20.23 REV 1 01.15.24 REV 2 03.28.24 REV 3 04.02.24 REV 4 (W/ADD ALT 1 SIGNAGE)</v>
+      <c r="J98" t="str" xml:space="preserve">
+        <v xml:space="preserve">01.06.23 03.20.23 REV 1
+ 01.15.24 REV 2
+ 03.28.24 REV 3
+ 04.02.24 REV 4
+ (W/ADD ALT 1 SIGNAGE)</v>
       </c>
       <c r="K98" t="str">
         <v>JEFFERSON LOYD PARK PH 1.</v>
@@ -4124,7 +4508,7 @@
         <v>2212JPI01S Jefferson Loyd Park Ph. 1 Signage REV 4.xlsx</v>
       </c>
     </row>
-    <row r="99">
+    <row r="99" xml:space="preserve">
       <c r="A99" t="str">
         <v xml:space="preserve">#10: BUILDING #7 (TYPE III) SIGNAGE </v>
       </c>
@@ -4152,8 +4536,12 @@
       <c r="I99" t="str">
         <v>2212JPI01S</v>
       </c>
-      <c r="J99" t="str">
-        <v>01.06.23 03.20.23 REV 1 01.15.24 REV 2 03.28.24 REV 3 04.02.24 REV 4 (W/ADD ALT 1 SIGNAGE)</v>
+      <c r="J99" t="str" xml:space="preserve">
+        <v xml:space="preserve">01.06.23 03.20.23 REV 1
+ 01.15.24 REV 2
+ 03.28.24 REV 3
+ 04.02.24 REV 4
+ (W/ADD ALT 1 SIGNAGE)</v>
       </c>
       <c r="K99" t="str">
         <v>JEFFERSON LOYD PARK PH 1.</v>
@@ -4162,7 +4550,7 @@
         <v>2212JPI01S Jefferson Loyd Park Ph. 1 Signage REV 4.xlsx</v>
       </c>
     </row>
-    <row r="100">
+    <row r="100" xml:space="preserve">
       <c r="A100" t="str">
         <v xml:space="preserve">#10: BUILDING #7 (TYPE III) SIGNAGE </v>
       </c>
@@ -4190,8 +4578,12 @@
       <c r="I100" t="str">
         <v>2212JPI01S</v>
       </c>
-      <c r="J100" t="str">
-        <v>01.06.23 03.20.23 REV 1 01.15.24 REV 2 03.28.24 REV 3 04.02.24 REV 4 (W/ADD ALT 1 SIGNAGE)</v>
+      <c r="J100" t="str" xml:space="preserve">
+        <v xml:space="preserve">01.06.23 03.20.23 REV 1
+ 01.15.24 REV 2
+ 03.28.24 REV 3
+ 04.02.24 REV 4
+ (W/ADD ALT 1 SIGNAGE)</v>
       </c>
       <c r="K100" t="str">
         <v>JEFFERSON LOYD PARK PH 1.</v>
@@ -4200,7 +4592,7 @@
         <v>2212JPI01S Jefferson Loyd Park Ph. 1 Signage REV 4.xlsx</v>
       </c>
     </row>
-    <row r="101">
+    <row r="101" xml:space="preserve">
       <c r="A101" t="str">
         <v xml:space="preserve">#10: BUILDING #7 (TYPE III) SIGNAGE </v>
       </c>
@@ -4228,8 +4620,12 @@
       <c r="I101" t="str">
         <v>2212JPI01S</v>
       </c>
-      <c r="J101" t="str">
-        <v>01.06.23 03.20.23 REV 1 01.15.24 REV 2 03.28.24 REV 3 04.02.24 REV 4 (W/ADD ALT 1 SIGNAGE)</v>
+      <c r="J101" t="str" xml:space="preserve">
+        <v xml:space="preserve">01.06.23 03.20.23 REV 1
+ 01.15.24 REV 2
+ 03.28.24 REV 3
+ 04.02.24 REV 4
+ (W/ADD ALT 1 SIGNAGE)</v>
       </c>
       <c r="K101" t="str">
         <v>JEFFERSON LOYD PARK PH 1.</v>
@@ -4238,7 +4634,7 @@
         <v>2212JPI01S Jefferson Loyd Park Ph. 1 Signage REV 4.xlsx</v>
       </c>
     </row>
-    <row r="102">
+    <row r="102" xml:space="preserve">
       <c r="A102" t="str">
         <v xml:space="preserve">#10: BUILDING #7 (TYPE III) SIGNAGE </v>
       </c>
@@ -4266,8 +4662,12 @@
       <c r="I102" t="str">
         <v>2212JPI01S</v>
       </c>
-      <c r="J102" t="str">
-        <v>01.06.23 03.20.23 REV 1 01.15.24 REV 2 03.28.24 REV 3 04.02.24 REV 4 (W/ADD ALT 1 SIGNAGE)</v>
+      <c r="J102" t="str" xml:space="preserve">
+        <v xml:space="preserve">01.06.23 03.20.23 REV 1
+ 01.15.24 REV 2
+ 03.28.24 REV 3
+ 04.02.24 REV 4
+ (W/ADD ALT 1 SIGNAGE)</v>
       </c>
       <c r="K102" t="str">
         <v>JEFFERSON LOYD PARK PH 1.</v>
@@ -4276,7 +4676,7 @@
         <v>2212JPI01S Jefferson Loyd Park Ph. 1 Signage REV 4.xlsx</v>
       </c>
     </row>
-    <row r="103">
+    <row r="103" xml:space="preserve">
       <c r="A103" t="str">
         <v xml:space="preserve">#10: BUILDING #7 (TYPE III) SIGNAGE </v>
       </c>
@@ -4304,8 +4704,12 @@
       <c r="I103" t="str">
         <v>2212JPI01S</v>
       </c>
-      <c r="J103" t="str">
-        <v>01.06.23 03.20.23 REV 1 01.15.24 REV 2 03.28.24 REV 3 04.02.24 REV 4 (W/ADD ALT 1 SIGNAGE)</v>
+      <c r="J103" t="str" xml:space="preserve">
+        <v xml:space="preserve">01.06.23 03.20.23 REV 1
+ 01.15.24 REV 2
+ 03.28.24 REV 3
+ 04.02.24 REV 4
+ (W/ADD ALT 1 SIGNAGE)</v>
       </c>
       <c r="K103" t="str">
         <v>JEFFERSON LOYD PARK PH 1.</v>
@@ -4314,7 +4718,7 @@
         <v>2212JPI01S Jefferson Loyd Park Ph. 1 Signage REV 4.xlsx</v>
       </c>
     </row>
-    <row r="104">
+    <row r="104" xml:space="preserve">
       <c r="A104" t="str">
         <v xml:space="preserve">#10: BUILDING #7 (TYPE III) SIGNAGE </v>
       </c>
@@ -4342,8 +4746,12 @@
       <c r="I104" t="str">
         <v>2212JPI01S</v>
       </c>
-      <c r="J104" t="str">
-        <v>01.06.23 03.20.23 REV 1 01.15.24 REV 2 03.28.24 REV 3 04.02.24 REV 4 (W/ADD ALT 1 SIGNAGE)</v>
+      <c r="J104" t="str" xml:space="preserve">
+        <v xml:space="preserve">01.06.23 03.20.23 REV 1
+ 01.15.24 REV 2
+ 03.28.24 REV 3
+ 04.02.24 REV 4
+ (W/ADD ALT 1 SIGNAGE)</v>
       </c>
       <c r="K104" t="str">
         <v>JEFFERSON LOYD PARK PH 1.</v>
@@ -4352,7 +4760,7 @@
         <v>2212JPI01S Jefferson Loyd Park Ph. 1 Signage REV 4.xlsx</v>
       </c>
     </row>
-    <row r="105">
+    <row r="105" xml:space="preserve">
       <c r="A105" t="str">
         <v xml:space="preserve">#11: BUILDING #8 (TYPE III) SIGNAGE </v>
       </c>
@@ -4380,8 +4788,12 @@
       <c r="I105" t="str">
         <v>2212JPI01S</v>
       </c>
-      <c r="J105" t="str">
-        <v>01.06.23 03.20.23 REV 1 01.15.24 REV 2 03.28.24 REV 3 04.02.24 REV 4 (W/ADD ALT 1 SIGNAGE)</v>
+      <c r="J105" t="str" xml:space="preserve">
+        <v xml:space="preserve">01.06.23 03.20.23 REV 1
+ 01.15.24 REV 2
+ 03.28.24 REV 3
+ 04.02.24 REV 4
+ (W/ADD ALT 1 SIGNAGE)</v>
       </c>
       <c r="K105" t="str">
         <v>JEFFERSON LOYD PARK PH 1.</v>
@@ -4390,7 +4802,7 @@
         <v>2212JPI01S Jefferson Loyd Park Ph. 1 Signage REV 4.xlsx</v>
       </c>
     </row>
-    <row r="106">
+    <row r="106" xml:space="preserve">
       <c r="A106" t="str">
         <v xml:space="preserve">#11: BUILDING #8 (TYPE III) SIGNAGE </v>
       </c>
@@ -4418,8 +4830,12 @@
       <c r="I106" t="str">
         <v>2212JPI01S</v>
       </c>
-      <c r="J106" t="str">
-        <v>01.06.23 03.20.23 REV 1 01.15.24 REV 2 03.28.24 REV 3 04.02.24 REV 4 (W/ADD ALT 1 SIGNAGE)</v>
+      <c r="J106" t="str" xml:space="preserve">
+        <v xml:space="preserve">01.06.23 03.20.23 REV 1
+ 01.15.24 REV 2
+ 03.28.24 REV 3
+ 04.02.24 REV 4
+ (W/ADD ALT 1 SIGNAGE)</v>
       </c>
       <c r="K106" t="str">
         <v>JEFFERSON LOYD PARK PH 1.</v>
@@ -4428,7 +4844,7 @@
         <v>2212JPI01S Jefferson Loyd Park Ph. 1 Signage REV 4.xlsx</v>
       </c>
     </row>
-    <row r="107">
+    <row r="107" xml:space="preserve">
       <c r="A107" t="str">
         <v xml:space="preserve">#11: BUILDING #8 (TYPE III) SIGNAGE </v>
       </c>
@@ -4456,8 +4872,12 @@
       <c r="I107" t="str">
         <v>2212JPI01S</v>
       </c>
-      <c r="J107" t="str">
-        <v>01.06.23 03.20.23 REV 1 01.15.24 REV 2 03.28.24 REV 3 04.02.24 REV 4 (W/ADD ALT 1 SIGNAGE)</v>
+      <c r="J107" t="str" xml:space="preserve">
+        <v xml:space="preserve">01.06.23 03.20.23 REV 1
+ 01.15.24 REV 2
+ 03.28.24 REV 3
+ 04.02.24 REV 4
+ (W/ADD ALT 1 SIGNAGE)</v>
       </c>
       <c r="K107" t="str">
         <v>JEFFERSON LOYD PARK PH 1.</v>
@@ -4466,7 +4886,7 @@
         <v>2212JPI01S Jefferson Loyd Park Ph. 1 Signage REV 4.xlsx</v>
       </c>
     </row>
-    <row r="108">
+    <row r="108" xml:space="preserve">
       <c r="A108" t="str">
         <v xml:space="preserve">#11: BUILDING #8 (TYPE III) SIGNAGE </v>
       </c>
@@ -4494,8 +4914,12 @@
       <c r="I108" t="str">
         <v>2212JPI01S</v>
       </c>
-      <c r="J108" t="str">
-        <v>01.06.23 03.20.23 REV 1 01.15.24 REV 2 03.28.24 REV 3 04.02.24 REV 4 (W/ADD ALT 1 SIGNAGE)</v>
+      <c r="J108" t="str" xml:space="preserve">
+        <v xml:space="preserve">01.06.23 03.20.23 REV 1
+ 01.15.24 REV 2
+ 03.28.24 REV 3
+ 04.02.24 REV 4
+ (W/ADD ALT 1 SIGNAGE)</v>
       </c>
       <c r="K108" t="str">
         <v>JEFFERSON LOYD PARK PH 1.</v>
@@ -4504,7 +4928,7 @@
         <v>2212JPI01S Jefferson Loyd Park Ph. 1 Signage REV 4.xlsx</v>
       </c>
     </row>
-    <row r="109">
+    <row r="109" xml:space="preserve">
       <c r="A109" t="str">
         <v xml:space="preserve">#11: BUILDING #8 (TYPE III) SIGNAGE </v>
       </c>
@@ -4532,8 +4956,12 @@
       <c r="I109" t="str">
         <v>2212JPI01S</v>
       </c>
-      <c r="J109" t="str">
-        <v>01.06.23 03.20.23 REV 1 01.15.24 REV 2 03.28.24 REV 3 04.02.24 REV 4 (W/ADD ALT 1 SIGNAGE)</v>
+      <c r="J109" t="str" xml:space="preserve">
+        <v xml:space="preserve">01.06.23 03.20.23 REV 1
+ 01.15.24 REV 2
+ 03.28.24 REV 3
+ 04.02.24 REV 4
+ (W/ADD ALT 1 SIGNAGE)</v>
       </c>
       <c r="K109" t="str">
         <v>JEFFERSON LOYD PARK PH 1.</v>
@@ -4542,7 +4970,7 @@
         <v>2212JPI01S Jefferson Loyd Park Ph. 1 Signage REV 4.xlsx</v>
       </c>
     </row>
-    <row r="110">
+    <row r="110" xml:space="preserve">
       <c r="A110" t="str">
         <v xml:space="preserve">#11: BUILDING #8 (TYPE III) SIGNAGE </v>
       </c>
@@ -4570,8 +4998,12 @@
       <c r="I110" t="str">
         <v>2212JPI01S</v>
       </c>
-      <c r="J110" t="str">
-        <v>01.06.23 03.20.23 REV 1 01.15.24 REV 2 03.28.24 REV 3 04.02.24 REV 4 (W/ADD ALT 1 SIGNAGE)</v>
+      <c r="J110" t="str" xml:space="preserve">
+        <v xml:space="preserve">01.06.23 03.20.23 REV 1
+ 01.15.24 REV 2
+ 03.28.24 REV 3
+ 04.02.24 REV 4
+ (W/ADD ALT 1 SIGNAGE)</v>
       </c>
       <c r="K110" t="str">
         <v>JEFFERSON LOYD PARK PH 1.</v>
@@ -4580,7 +5012,7 @@
         <v>2212JPI01S Jefferson Loyd Park Ph. 1 Signage REV 4.xlsx</v>
       </c>
     </row>
-    <row r="111">
+    <row r="111" xml:space="preserve">
       <c r="A111" t="str">
         <v xml:space="preserve">#11: BUILDING #8 (TYPE III) SIGNAGE </v>
       </c>
@@ -4608,8 +5040,12 @@
       <c r="I111" t="str">
         <v>2212JPI01S</v>
       </c>
-      <c r="J111" t="str">
-        <v>01.06.23 03.20.23 REV 1 01.15.24 REV 2 03.28.24 REV 3 04.02.24 REV 4 (W/ADD ALT 1 SIGNAGE)</v>
+      <c r="J111" t="str" xml:space="preserve">
+        <v xml:space="preserve">01.06.23 03.20.23 REV 1
+ 01.15.24 REV 2
+ 03.28.24 REV 3
+ 04.02.24 REV 4
+ (W/ADD ALT 1 SIGNAGE)</v>
       </c>
       <c r="K111" t="str">
         <v>JEFFERSON LOYD PARK PH 1.</v>
@@ -4618,7 +5054,7 @@
         <v>2212JPI01S Jefferson Loyd Park Ph. 1 Signage REV 4.xlsx</v>
       </c>
     </row>
-    <row r="112">
+    <row r="112" xml:space="preserve">
       <c r="A112" t="str">
         <v xml:space="preserve">#11: BUILDING #8 (TYPE III) SIGNAGE </v>
       </c>
@@ -4646,8 +5082,12 @@
       <c r="I112" t="str">
         <v>2212JPI01S</v>
       </c>
-      <c r="J112" t="str">
-        <v>01.06.23 03.20.23 REV 1 01.15.24 REV 2 03.28.24 REV 3 04.02.24 REV 4 (W/ADD ALT 1 SIGNAGE)</v>
+      <c r="J112" t="str" xml:space="preserve">
+        <v xml:space="preserve">01.06.23 03.20.23 REV 1
+ 01.15.24 REV 2
+ 03.28.24 REV 3
+ 04.02.24 REV 4
+ (W/ADD ALT 1 SIGNAGE)</v>
       </c>
       <c r="K112" t="str">
         <v>JEFFERSON LOYD PARK PH 1.</v>
@@ -4656,7 +5096,7 @@
         <v>2212JPI01S Jefferson Loyd Park Ph. 1 Signage REV 4.xlsx</v>
       </c>
     </row>
-    <row r="113">
+    <row r="113" xml:space="preserve">
       <c r="A113" t="str">
         <v xml:space="preserve">#11: BUILDING #8 (TYPE III) SIGNAGE </v>
       </c>
@@ -4684,8 +5124,12 @@
       <c r="I113" t="str">
         <v>2212JPI01S</v>
       </c>
-      <c r="J113" t="str">
-        <v>01.06.23 03.20.23 REV 1 01.15.24 REV 2 03.28.24 REV 3 04.02.24 REV 4 (W/ADD ALT 1 SIGNAGE)</v>
+      <c r="J113" t="str" xml:space="preserve">
+        <v xml:space="preserve">01.06.23 03.20.23 REV 1
+ 01.15.24 REV 2
+ 03.28.24 REV 3
+ 04.02.24 REV 4
+ (W/ADD ALT 1 SIGNAGE)</v>
       </c>
       <c r="K113" t="str">
         <v>JEFFERSON LOYD PARK PH 1.</v>
@@ -4694,7 +5138,7 @@
         <v>2212JPI01S Jefferson Loyd Park Ph. 1 Signage REV 4.xlsx</v>
       </c>
     </row>
-    <row r="114">
+    <row r="114" xml:space="preserve">
       <c r="A114" t="str">
         <v xml:space="preserve">#11: BUILDING #8 (TYPE III) SIGNAGE </v>
       </c>
@@ -4722,8 +5166,12 @@
       <c r="I114" t="str">
         <v>2212JPI01S</v>
       </c>
-      <c r="J114" t="str">
-        <v>01.06.23 03.20.23 REV 1 01.15.24 REV 2 03.28.24 REV 3 04.02.24 REV 4 (W/ADD ALT 1 SIGNAGE)</v>
+      <c r="J114" t="str" xml:space="preserve">
+        <v xml:space="preserve">01.06.23 03.20.23 REV 1
+ 01.15.24 REV 2
+ 03.28.24 REV 3
+ 04.02.24 REV 4
+ (W/ADD ALT 1 SIGNAGE)</v>
       </c>
       <c r="K114" t="str">
         <v>JEFFERSON LOYD PARK PH 1.</v>
@@ -4732,7 +5180,7 @@
         <v>2212JPI01S Jefferson Loyd Park Ph. 1 Signage REV 4.xlsx</v>
       </c>
     </row>
-    <row r="115">
+    <row r="115" xml:space="preserve">
       <c r="A115" t="str">
         <v xml:space="preserve">#11: BUILDING #8 (TYPE III) SIGNAGE </v>
       </c>
@@ -4760,8 +5208,12 @@
       <c r="I115" t="str">
         <v>2212JPI01S</v>
       </c>
-      <c r="J115" t="str">
-        <v>01.06.23 03.20.23 REV 1 01.15.24 REV 2 03.28.24 REV 3 04.02.24 REV 4 (W/ADD ALT 1 SIGNAGE)</v>
+      <c r="J115" t="str" xml:space="preserve">
+        <v xml:space="preserve">01.06.23 03.20.23 REV 1
+ 01.15.24 REV 2
+ 03.28.24 REV 3
+ 04.02.24 REV 4
+ (W/ADD ALT 1 SIGNAGE)</v>
       </c>
       <c r="K115" t="str">
         <v>JEFFERSON LOYD PARK PH 1.</v>
@@ -4770,7 +5222,7 @@
         <v>2212JPI01S Jefferson Loyd Park Ph. 1 Signage REV 4.xlsx</v>
       </c>
     </row>
-    <row r="116">
+    <row r="116" xml:space="preserve">
       <c r="A116" t="str">
         <v xml:space="preserve">#11: BUILDING #8 (TYPE III) SIGNAGE </v>
       </c>
@@ -4798,8 +5250,12 @@
       <c r="I116" t="str">
         <v>2212JPI01S</v>
       </c>
-      <c r="J116" t="str">
-        <v>01.06.23 03.20.23 REV 1 01.15.24 REV 2 03.28.24 REV 3 04.02.24 REV 4 (W/ADD ALT 1 SIGNAGE)</v>
+      <c r="J116" t="str" xml:space="preserve">
+        <v xml:space="preserve">01.06.23 03.20.23 REV 1
+ 01.15.24 REV 2
+ 03.28.24 REV 3
+ 04.02.24 REV 4
+ (W/ADD ALT 1 SIGNAGE)</v>
       </c>
       <c r="K116" t="str">
         <v>JEFFERSON LOYD PARK PH 1.</v>
@@ -4808,7 +5264,7 @@
         <v>2212JPI01S Jefferson Loyd Park Ph. 1 Signage REV 4.xlsx</v>
       </c>
     </row>
-    <row r="117">
+    <row r="117" xml:space="preserve">
       <c r="A117" t="str">
         <v xml:space="preserve">#12: AMENITY SIGNAGE </v>
       </c>
@@ -4836,8 +5292,12 @@
       <c r="I117" t="str">
         <v>2212JPI01S</v>
       </c>
-      <c r="J117" t="str">
-        <v>01.06.23 03.20.23 REV 1 01.15.24 REV 2 03.28.24 REV 3 04.02.24 REV 4 (W/ADD ALT 1 SIGNAGE)</v>
+      <c r="J117" t="str" xml:space="preserve">
+        <v xml:space="preserve">01.06.23 03.20.23 REV 1
+ 01.15.24 REV 2
+ 03.28.24 REV 3
+ 04.02.24 REV 4
+ (W/ADD ALT 1 SIGNAGE)</v>
       </c>
       <c r="K117" t="str">
         <v>JEFFERSON LOYD PARK PH 1.</v>
@@ -4846,7 +5306,7 @@
         <v>2212JPI01S Jefferson Loyd Park Ph. 1 Signage REV 4.xlsx</v>
       </c>
     </row>
-    <row r="118">
+    <row r="118" xml:space="preserve">
       <c r="A118" t="str">
         <v xml:space="preserve">#12: AMENITY SIGNAGE </v>
       </c>
@@ -4874,8 +5334,12 @@
       <c r="I118" t="str">
         <v>2212JPI01S</v>
       </c>
-      <c r="J118" t="str">
-        <v>01.06.23 03.20.23 REV 1 01.15.24 REV 2 03.28.24 REV 3 04.02.24 REV 4 (W/ADD ALT 1 SIGNAGE)</v>
+      <c r="J118" t="str" xml:space="preserve">
+        <v xml:space="preserve">01.06.23 03.20.23 REV 1
+ 01.15.24 REV 2
+ 03.28.24 REV 3
+ 04.02.24 REV 4
+ (W/ADD ALT 1 SIGNAGE)</v>
       </c>
       <c r="K118" t="str">
         <v>JEFFERSON LOYD PARK PH 1.</v>
@@ -4884,7 +5348,7 @@
         <v>2212JPI01S Jefferson Loyd Park Ph. 1 Signage REV 4.xlsx</v>
       </c>
     </row>
-    <row r="119">
+    <row r="119" xml:space="preserve">
       <c r="A119" t="str">
         <v xml:space="preserve">#12: AMENITY SIGNAGE </v>
       </c>
@@ -4912,8 +5376,12 @@
       <c r="I119" t="str">
         <v>2212JPI01S</v>
       </c>
-      <c r="J119" t="str">
-        <v>01.06.23 03.20.23 REV 1 01.15.24 REV 2 03.28.24 REV 3 04.02.24 REV 4 (W/ADD ALT 1 SIGNAGE)</v>
+      <c r="J119" t="str" xml:space="preserve">
+        <v xml:space="preserve">01.06.23 03.20.23 REV 1
+ 01.15.24 REV 2
+ 03.28.24 REV 3
+ 04.02.24 REV 4
+ (W/ADD ALT 1 SIGNAGE)</v>
       </c>
       <c r="K119" t="str">
         <v>JEFFERSON LOYD PARK PH 1.</v>
@@ -4922,7 +5390,7 @@
         <v>2212JPI01S Jefferson Loyd Park Ph. 1 Signage REV 4.xlsx</v>
       </c>
     </row>
-    <row r="120">
+    <row r="120" xml:space="preserve">
       <c r="A120" t="str">
         <v xml:space="preserve">#12: AMENITY SIGNAGE </v>
       </c>
@@ -4950,8 +5418,12 @@
       <c r="I120" t="str">
         <v>2212JPI01S</v>
       </c>
-      <c r="J120" t="str">
-        <v>01.06.23 03.20.23 REV 1 01.15.24 REV 2 03.28.24 REV 3 04.02.24 REV 4 (W/ADD ALT 1 SIGNAGE)</v>
+      <c r="J120" t="str" xml:space="preserve">
+        <v xml:space="preserve">01.06.23 03.20.23 REV 1
+ 01.15.24 REV 2
+ 03.28.24 REV 3
+ 04.02.24 REV 4
+ (W/ADD ALT 1 SIGNAGE)</v>
       </c>
       <c r="K120" t="str">
         <v>JEFFERSON LOYD PARK PH 1.</v>
@@ -4960,7 +5432,7 @@
         <v>2212JPI01S Jefferson Loyd Park Ph. 1 Signage REV 4.xlsx</v>
       </c>
     </row>
-    <row r="121">
+    <row r="121" xml:space="preserve">
       <c r="A121" t="str">
         <v xml:space="preserve">#12: AMENITY SIGNAGE </v>
       </c>
@@ -4988,8 +5460,12 @@
       <c r="I121" t="str">
         <v>2212JPI01S</v>
       </c>
-      <c r="J121" t="str">
-        <v>01.06.23 03.20.23 REV 1 01.15.24 REV 2 03.28.24 REV 3 04.02.24 REV 4 (W/ADD ALT 1 SIGNAGE)</v>
+      <c r="J121" t="str" xml:space="preserve">
+        <v xml:space="preserve">01.06.23 03.20.23 REV 1
+ 01.15.24 REV 2
+ 03.28.24 REV 3
+ 04.02.24 REV 4
+ (W/ADD ALT 1 SIGNAGE)</v>
       </c>
       <c r="K121" t="str">
         <v>JEFFERSON LOYD PARK PH 1.</v>
@@ -4998,7 +5474,7 @@
         <v>2212JPI01S Jefferson Loyd Park Ph. 1 Signage REV 4.xlsx</v>
       </c>
     </row>
-    <row r="122">
+    <row r="122" xml:space="preserve">
       <c r="A122" t="str">
         <v xml:space="preserve">#12: AMENITY SIGNAGE </v>
       </c>
@@ -5026,8 +5502,12 @@
       <c r="I122" t="str">
         <v>2212JPI01S</v>
       </c>
-      <c r="J122" t="str">
-        <v>01.06.23 03.20.23 REV 1 01.15.24 REV 2 03.28.24 REV 3 04.02.24 REV 4 (W/ADD ALT 1 SIGNAGE)</v>
+      <c r="J122" t="str" xml:space="preserve">
+        <v xml:space="preserve">01.06.23 03.20.23 REV 1
+ 01.15.24 REV 2
+ 03.28.24 REV 3
+ 04.02.24 REV 4
+ (W/ADD ALT 1 SIGNAGE)</v>
       </c>
       <c r="K122" t="str">
         <v>JEFFERSON LOYD PARK PH 1.</v>
@@ -5036,7 +5516,7 @@
         <v>2212JPI01S Jefferson Loyd Park Ph. 1 Signage REV 4.xlsx</v>
       </c>
     </row>
-    <row r="123">
+    <row r="123" xml:space="preserve">
       <c r="A123" t="str">
         <v xml:space="preserve">#12: AMENITY SIGNAGE </v>
       </c>
@@ -5064,8 +5544,12 @@
       <c r="I123" t="str">
         <v>2212JPI01S</v>
       </c>
-      <c r="J123" t="str">
-        <v>01.06.23 03.20.23 REV 1 01.15.24 REV 2 03.28.24 REV 3 04.02.24 REV 4 (W/ADD ALT 1 SIGNAGE)</v>
+      <c r="J123" t="str" xml:space="preserve">
+        <v xml:space="preserve">01.06.23 03.20.23 REV 1
+ 01.15.24 REV 2
+ 03.28.24 REV 3
+ 04.02.24 REV 4
+ (W/ADD ALT 1 SIGNAGE)</v>
       </c>
       <c r="K123" t="str">
         <v>JEFFERSON LOYD PARK PH 1.</v>
@@ -5074,7 +5558,7 @@
         <v>2212JPI01S Jefferson Loyd Park Ph. 1 Signage REV 4.xlsx</v>
       </c>
     </row>
-    <row r="124">
+    <row r="124" xml:space="preserve">
       <c r="A124" t="str">
         <v xml:space="preserve">#12: AMENITY SIGNAGE </v>
       </c>
@@ -5102,8 +5586,12 @@
       <c r="I124" t="str">
         <v>2212JPI01S</v>
       </c>
-      <c r="J124" t="str">
-        <v>01.06.23 03.20.23 REV 1 01.15.24 REV 2 03.28.24 REV 3 04.02.24 REV 4 (W/ADD ALT 1 SIGNAGE)</v>
+      <c r="J124" t="str" xml:space="preserve">
+        <v xml:space="preserve">01.06.23 03.20.23 REV 1
+ 01.15.24 REV 2
+ 03.28.24 REV 3
+ 04.02.24 REV 4
+ (W/ADD ALT 1 SIGNAGE)</v>
       </c>
       <c r="K124" t="str">
         <v>JEFFERSON LOYD PARK PH 1.</v>
@@ -5112,7 +5600,7 @@
         <v>2212JPI01S Jefferson Loyd Park Ph. 1 Signage REV 4.xlsx</v>
       </c>
     </row>
-    <row r="125">
+    <row r="125" xml:space="preserve">
       <c r="A125" t="str">
         <v xml:space="preserve">#12: AMENITY SIGNAGE </v>
       </c>
@@ -5140,8 +5628,12 @@
       <c r="I125" t="str">
         <v>2212JPI01S</v>
       </c>
-      <c r="J125" t="str">
-        <v>01.06.23 03.20.23 REV 1 01.15.24 REV 2 03.28.24 REV 3 04.02.24 REV 4 (W/ADD ALT 1 SIGNAGE)</v>
+      <c r="J125" t="str" xml:space="preserve">
+        <v xml:space="preserve">01.06.23 03.20.23 REV 1
+ 01.15.24 REV 2
+ 03.28.24 REV 3
+ 04.02.24 REV 4
+ (W/ADD ALT 1 SIGNAGE)</v>
       </c>
       <c r="K125" t="str">
         <v>JEFFERSON LOYD PARK PH 1.</v>
